--- a/inventory_master.xlsx
+++ b/inventory_master.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,8 +42,24 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00375623"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -63,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00BDD7EE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,6 +126,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -487,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:O240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -503,6 +533,8 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
@@ -531,6 +563,8 @@
           <t>CNT-003</t>
         </is>
       </c>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -596,6 +630,16 @@
       <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Presale QTY</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>Serial Number</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
         </is>
       </c>
     </row>
@@ -651,346 +695,391 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
+    <row r="4">
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0001</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0002</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0003</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0004</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="8"/>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J9" s="5">
-        <f>F9+G9+H9-I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="9" ht="16" customHeight="1"/>
     <row r="10"/>
     <row r="11"/>
     <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J13" s="5">
+        <f>F9+G9+H9-I9</f>
+        <v/>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0005</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Right Outswing</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="H15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J15" s="5">
-        <f>F15+G15+H15-I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M15" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I21" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="5">
-        <f>F21+G21+H21-I21</f>
-        <v/>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0006</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0007</t>
+        </is>
+      </c>
+      <c r="O16" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0008</t>
+        </is>
+      </c>
+      <c r="O17" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0009</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0010</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>24-0315-0011</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1"/>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
     <row r="25"/>
-    <row r="26"/>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Oil-Rubbed Bronze</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>Right Outswing</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" s="5">
+        <f>F15+G15+H15-I15</f>
+        <v/>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M26" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" s="5">
-        <f>F27+G27+H27-I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28"/>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>24-0721-0012</t>
+        </is>
+      </c>
+      <c r="O27" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>24-0721-0013</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="29"/>
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Cordova</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="33" ht="16" customHeight="1"/>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="5" t="n">
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I33" s="5" t="n">
+      <c r="I34" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J33" s="5">
-        <f>F33+G33+H33-I33</f>
+      <c r="J34" s="5">
+        <f>F21+G21+H21-I21</f>
         <v/>
       </c>
-      <c r="K33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
+      <c r="K34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>24-1102-0014</t>
+        </is>
+      </c>
+      <c r="O35" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>24-1102-0015</t>
+        </is>
+      </c>
+      <c r="O36" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>24-1102-0016</t>
+        </is>
+      </c>
+      <c r="O37" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>24-1102-0017</t>
+        </is>
+      </c>
+      <c r="O38" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Cordova</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="J39" s="5">
-        <f>F39+G39+H39-I39</f>
-        <v/>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v>1</v>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>24-1102-0018</t>
+        </is>
+      </c>
+      <c r="O39" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
       </c>
     </row>
     <row r="40"/>
@@ -1001,281 +1090,311 @@
     <row r="45" ht="16" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>Cordova</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>36" x 96"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Right Outswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" s="5">
+        <f>F27+G27+H27-I27</f>
+        <v/>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G45" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="5">
-        <f>F45+G45+H45-I45</f>
-        <v/>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="M45" s="5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
+    <row r="46">
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>24-1102-0019</t>
+        </is>
+      </c>
+      <c r="O46" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>24-1102-0020</t>
+        </is>
+      </c>
+      <c r="O47" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>24-1102-0021</t>
+        </is>
+      </c>
+      <c r="O48" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="49"/>
     <row r="50"/>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C51" s="4" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J51" s="5">
-        <f>F51+G51+H51-I51</f>
-        <v/>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="51" ht="16" customHeight="1"/>
     <row r="52"/>
     <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Cordova</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" s="5">
+        <f>F33+G33+H33-I33</f>
+        <v/>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>25-0210-0001</t>
+        </is>
+      </c>
+      <c r="O55" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>25-0210-0002</t>
+        </is>
+      </c>
+      <c r="O56" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>Sidelite</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J57" s="5">
-        <f>F57+G57+H57-I57</f>
-        <v/>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>25-0210-0003</t>
+        </is>
+      </c>
+      <c r="O57" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>25-0210-0004</t>
+        </is>
+      </c>
+      <c r="O58" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>25-0210-0005</t>
+        </is>
+      </c>
+      <c r="O59" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>25-0210-0006</t>
+        </is>
+      </c>
+      <c r="O60" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="61"/>
     <row r="62"/>
-    <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
-      <c r="B63" s="4" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C63" s="4" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="J63" s="5">
-        <f>F63+G63+H63-I63</f>
-        <v/>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="63" ht="16" customHeight="1"/>
     <row r="64"/>
     <row r="65"/>
-    <row r="66"/>
-    <row r="67"/>
-    <row r="68"/>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Cordova</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Oil-Rubbed Bronze</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="J66" s="5">
+        <f>F39+G39+H39-I39</f>
+        <v/>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>25-0518-0007</t>
+        </is>
+      </c>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>25-0518-0008</t>
+        </is>
+      </c>
+      <c r="O68" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H69" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I69" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="J69" s="5">
-        <f>F69+G69+H69-I69</f>
-        <v/>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v>0</v>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>25-0518-0009</t>
+        </is>
+      </c>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
       </c>
     </row>
     <row r="70"/>
@@ -1286,169 +1405,841 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Altea</t>
+          <t>Cordova</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 96"</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Right Outswing</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Clear</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="F75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G75" s="5" t="n">
+      <c r="H75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" s="5">
+        <f>F45+G45+H45-I45</f>
+        <v/>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H75" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J75" s="5">
-        <f>F75+G75+H75-I75</f>
-        <v/>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="M75" s="5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="76"/>
+    <row r="76">
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>25-0518-0010</t>
+        </is>
+      </c>
+      <c r="O76" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
     <row r="77"/>
     <row r="78"/>
     <row r="79"/>
     <row r="80"/>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="81" ht="16" customHeight="1"/>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" s="5">
+        <f>F51+G51+H51-I51</f>
+        <v/>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0011</t>
+        </is>
+      </c>
+      <c r="O83" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0012</t>
+        </is>
+      </c>
+      <c r="O84" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0013</t>
+        </is>
+      </c>
+      <c r="O85" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0014</t>
+        </is>
+      </c>
+      <c r="O86" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0015</t>
+        </is>
+      </c>
+      <c r="O87" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0016</t>
+        </is>
+      </c>
+      <c r="O88" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0017</t>
+        </is>
+      </c>
+      <c r="O89" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0018</t>
+        </is>
+      </c>
+      <c r="O90" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Sidelite</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J96" s="5">
+        <f>F57+G57+H57-I57</f>
+        <v/>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0019</t>
+        </is>
+      </c>
+      <c r="O97" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="N98" s="7" t="inlineStr">
+        <is>
+          <t>25-0927-0020</t>
+        </is>
+      </c>
+      <c r="O98" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="99"/>
+    <row r="100"/>
+    <row r="101"/>
+    <row r="102"/>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H104" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I104" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J104" s="5">
+        <f>F63+G63+H63-I63</f>
+        <v/>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="N105" s="7" t="inlineStr">
+        <is>
+          <t>25-1205-0021</t>
+        </is>
+      </c>
+      <c r="O105" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="N106" s="7" t="inlineStr">
+        <is>
+          <t>25-1205-0022</t>
+        </is>
+      </c>
+      <c r="O106" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="N107" s="7" t="inlineStr">
+        <is>
+          <t>25-1205-0023</t>
+        </is>
+      </c>
+      <c r="O107" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="N108" s="7" t="inlineStr">
+        <is>
+          <t>25-1205-0024</t>
+        </is>
+      </c>
+      <c r="O108" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="109"/>
+    <row r="110"/>
+    <row r="111"/>
+    <row r="112"/>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Oil-Rubbed Bronze</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H114" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="J114" s="5">
+        <f>F69+G69+H69-I69</f>
+        <v/>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="M114" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115"/>
+    <row r="116"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J120" s="5">
+        <f>F75+G75+H75-I75</f>
+        <v/>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" s="5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="N121" s="7" t="inlineStr">
+        <is>
+          <t>26-0103-0001</t>
+        </is>
+      </c>
+      <c r="O121" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="N122" s="7" t="inlineStr">
+        <is>
+          <t>26-0103-0002</t>
+        </is>
+      </c>
+      <c r="O122" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="N123" s="7" t="inlineStr">
+        <is>
+          <t>26-0103-0003</t>
+        </is>
+      </c>
+      <c r="O123" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="N124" s="7" t="inlineStr">
+        <is>
+          <t>26-0103-0004</t>
+        </is>
+      </c>
+      <c r="O124" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="N125" s="7" t="inlineStr">
+        <is>
+          <t>26-0103-0005</t>
+        </is>
+      </c>
+      <c r="O125" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D131" s="4" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F131" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H81" s="5" t="n">
+      <c r="G131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="I81" s="5" t="n">
+      <c r="I131" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="J81" s="5">
+      <c r="J131" s="5">
         <f>F81+G81+H81-I81</f>
         <v/>
       </c>
-      <c r="K81" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="5" t="n">
+      <c r="K131" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M81" s="5" t="n">
+      <c r="M131" s="5" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="4" t="inlineStr">
+    <row r="132">
+      <c r="N132" s="7" t="inlineStr">
+        <is>
+          <t>26-0103-0006</t>
+        </is>
+      </c>
+      <c r="O132" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="N133" s="7" t="inlineStr">
+        <is>
+          <t>26-0103-0007</t>
+        </is>
+      </c>
+      <c r="O133" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="N134" s="7" t="inlineStr">
+        <is>
+          <t>26-0103-0008</t>
+        </is>
+      </c>
+      <c r="O134" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B140" s="4" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C140" s="4" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D140" s="4" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="E140" s="4" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F140" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G87" s="5" t="n">
+      <c r="G140" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H87" s="5" t="n">
+      <c r="H140" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="I87" s="5" t="n">
+      <c r="I140" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="J87" s="5">
+      <c r="J140" s="5">
         <f>F87+G87+H87-I87</f>
         <v/>
       </c>
-      <c r="K87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="5" t="n">
+      <c r="K140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" s="5" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="141">
+      <c r="N141" s="7" t="inlineStr">
+        <is>
+          <t>26-0415-0009</t>
+        </is>
+      </c>
+      <c r="O141" s="8" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
+    <row r="145"/>
+    <row r="146"/>
+    <row r="147"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
+    <row r="151"/>
+    <row r="152"/>
+    <row r="153"/>
+    <row r="154"/>
+    <row r="155"/>
+    <row r="156"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
+    <row r="160"/>
+    <row r="161"/>
+    <row r="162"/>
+    <row r="163"/>
+    <row r="164"/>
+    <row r="165"/>
+    <row r="166"/>
+    <row r="167"/>
+    <row r="168"/>
+    <row r="169"/>
+    <row r="170"/>
+    <row r="171"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
+    <row r="175"/>
+    <row r="176"/>
+    <row r="177"/>
+    <row r="178"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
+    <row r="182"/>
+    <row r="183"/>
+    <row r="184"/>
+    <row r="185"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
+    <row r="189"/>
+    <row r="190"/>
+    <row r="191"/>
+    <row r="192"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198"/>
+    <row r="199"/>
+    <row r="200"/>
+    <row r="201"/>
+    <row r="202"/>
+    <row r="203"/>
+    <row r="204"/>
+    <row r="205"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
+    <row r="209"/>
+    <row r="210"/>
+    <row r="211"/>
+    <row r="212"/>
+    <row r="213"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
+    <row r="217"/>
+    <row r="218"/>
+    <row r="219"/>
+    <row r="220"/>
+    <row r="221"/>
+    <row r="222"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
+    <row r="229"/>
+    <row r="230"/>
+    <row r="231"/>
+    <row r="232"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
+    <row r="236"/>
+    <row r="237"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
   </sheetData>
   <conditionalFormatting sqref="J3:J87">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">

--- a/inventory_master.xlsx
+++ b/inventory_master.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,6 +34,11 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -48,7 +53,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -70,11 +75,123 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00404040"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="00404040"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="medium">
+        <color rgb="00404040"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="00404040"/>
+      </right>
+      <top style="medium">
+        <color rgb="00404040"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00404040"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="00404040"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00404040"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00404040"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00404040"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="medium">
+        <color rgb="00404040"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00404040"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -85,11 +202,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="9">
     <dxf>
       <font>
         <name val="Arial"/>
@@ -135,6 +288,66 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00BDD7EE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="FFC00000"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <color rgb="FF000000"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFBDD7EE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -580,3041 +793,3046 @@
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="6">
         <f>COUNTIFS($A:$A,A2,$B:$B,B2,$C:$C,C2,$D:$D,D2,$E:$E,E2,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="6">
         <f>COUNTIFS($A:$A,A2,$B:$B,B2,$C:$C,C2,$D:$D,D2,$E:$E,E2,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="6">
         <f>COUNTIFS($A:$A,A2,$B:$B,B2,$C:$C,C2,$D:$D,D2,$E:$E,E2,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="6">
         <f>F2+G2+H2-I2</f>
         <v/>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>24-0315-0001</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="10">
         <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="10">
         <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="10">
         <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="10">
         <f>F3+G3+H3-I3</f>
         <v/>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="10" t="inlineStr">
         <is>
           <t>24-0315-0002</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="10">
         <f>COUNTIFS($A:$A,A4,$B:$B,B4,$C:$C,C4,$D:$D,D4,$E:$E,E4,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="10">
         <f>COUNTIFS($A:$A,A4,$B:$B,B4,$C:$C,C4,$D:$D,D4,$E:$E,E4,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="10">
         <f>COUNTIFS($A:$A,A4,$B:$B,B4,$C:$C,C4,$D:$D,D4,$E:$E,E4,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="10">
         <f>F4+G4+H4-I4</f>
         <v/>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>24-0315-0003</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="10">
         <f>COUNTIFS($A:$A,A5,$B:$B,B5,$C:$C,C5,$D:$D,D5,$E:$E,E5,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="10">
         <f>COUNTIFS($A:$A,A5,$B:$B,B5,$C:$C,C5,$D:$D,D5,$E:$E,E5,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="10">
         <f>COUNTIFS($A:$A,A5,$B:$B,B5,$C:$C,C5,$D:$D,D5,$E:$E,E5,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J5" s="3">
+      <c r="J5" s="10">
         <f>F5+G5+H5-I5</f>
         <v/>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K5" s="10" t="inlineStr">
         <is>
           <t>24-0315-0004</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L5" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="10">
         <f>COUNTIFS($A:$A,A6,$B:$B,B6,$C:$C,C6,$D:$D,D6,$E:$E,E6,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="10">
         <f>COUNTIFS($A:$A,A6,$B:$B,B6,$C:$C,C6,$D:$D,D6,$E:$E,E6,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H6" s="3">
+      <c r="H6" s="10">
         <f>COUNTIFS($A:$A,A6,$B:$B,B6,$C:$C,C6,$D:$D,D6,$E:$E,E6,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="10">
         <f>F6+G6+H6-I6</f>
         <v/>
       </c>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>24-0315-0005</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="L6" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F7" s="3">
+      <c r="F7" s="10">
         <f>COUNTIFS($A:$A,A7,$B:$B,B7,$C:$C,C7,$D:$D,D7,$E:$E,E7,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="10">
         <f>COUNTIFS($A:$A,A7,$B:$B,B7,$C:$C,C7,$D:$D,D7,$E:$E,E7,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="10">
         <f>COUNTIFS($A:$A,A7,$B:$B,B7,$C:$C,C7,$D:$D,D7,$E:$E,E7,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J7" s="3">
+      <c r="J7" s="10">
         <f>F7+G7+H7-I7</f>
         <v/>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="K7" s="10" t="inlineStr">
         <is>
           <t>24-0315-0006</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="L7" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F8" s="3">
+      <c r="F8" s="10">
         <f>COUNTIFS($A:$A,A8,$B:$B,B8,$C:$C,C8,$D:$D,D8,$E:$E,E8,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="10">
         <f>COUNTIFS($A:$A,A8,$B:$B,B8,$C:$C,C8,$D:$D,D8,$E:$E,E8,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H8" s="3">
+      <c r="H8" s="10">
         <f>COUNTIFS($A:$A,A8,$B:$B,B8,$C:$C,C8,$D:$D,D8,$E:$E,E8,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="3">
+      <c r="J8" s="10">
         <f>F8+G8+H8-I8</f>
         <v/>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="K8" s="10" t="inlineStr">
         <is>
           <t>24-0315-0007</t>
         </is>
       </c>
-      <c r="L8" s="3" t="inlineStr">
+      <c r="L8" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="10">
         <f>COUNTIFS($A:$A,A9,$B:$B,B9,$C:$C,C9,$D:$D,D9,$E:$E,E9,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="10">
         <f>COUNTIFS($A:$A,A9,$B:$B,B9,$C:$C,C9,$D:$D,D9,$E:$E,E9,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="10">
         <f>COUNTIFS($A:$A,A9,$B:$B,B9,$C:$C,C9,$D:$D,D9,$E:$E,E9,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="3">
+      <c r="J9" s="10">
         <f>F9+G9+H9-I9</f>
         <v/>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="K9" s="10" t="inlineStr">
         <is>
           <t>24-0315-0008</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="L9" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="10">
         <f>COUNTIFS($A:$A,A10,$B:$B,B10,$C:$C,C10,$D:$D,D10,$E:$E,E10,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="10">
         <f>COUNTIFS($A:$A,A10,$B:$B,B10,$C:$C,C10,$D:$D,D10,$E:$E,E10,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="10">
         <f>COUNTIFS($A:$A,A10,$B:$B,B10,$C:$C,C10,$D:$D,D10,$E:$E,E10,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="3">
+      <c r="J10" s="10">
         <f>F10+G10+H10-I10</f>
         <v/>
       </c>
-      <c r="K10" s="3" t="inlineStr">
+      <c r="K10" s="10" t="inlineStr">
         <is>
           <t>24-0315-0009</t>
         </is>
       </c>
-      <c r="L10" s="3" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="10">
         <f>COUNTIFS($A:$A,A11,$B:$B,B11,$C:$C,C11,$D:$D,D11,$E:$E,E11,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="10">
         <f>COUNTIFS($A:$A,A11,$B:$B,B11,$C:$C,C11,$D:$D,D11,$E:$E,E11,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H11" s="3">
+      <c r="H11" s="10">
         <f>COUNTIFS($A:$A,A11,$B:$B,B11,$C:$C,C11,$D:$D,D11,$E:$E,E11,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="3">
+      <c r="J11" s="10">
         <f>F11+G11+H11-I11</f>
         <v/>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="K11" s="10" t="inlineStr">
         <is>
           <t>24-0315-0010</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="L11" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F12" s="3">
+      <c r="F12" s="10">
         <f>COUNTIFS($A:$A,A12,$B:$B,B12,$C:$C,C12,$D:$D,D12,$E:$E,E12,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="10">
         <f>COUNTIFS($A:$A,A12,$B:$B,B12,$C:$C,C12,$D:$D,D12,$E:$E,E12,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="10">
         <f>COUNTIFS($A:$A,A12,$B:$B,B12,$C:$C,C12,$D:$D,D12,$E:$E,E12,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="10">
         <f>F12+G12+H12-I12</f>
         <v/>
       </c>
-      <c r="K12" s="3" t="inlineStr">
+      <c r="K12" s="10" t="inlineStr">
         <is>
           <t>24-0315-0011</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr">
+      <c r="L12" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="10">
         <f>COUNTIFS($A:$A,A13,$B:$B,B13,$C:$C,C13,$D:$D,D13,$E:$E,E13,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="10">
         <f>COUNTIFS($A:$A,A13,$B:$B,B13,$C:$C,C13,$D:$D,D13,$E:$E,E13,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="10">
         <f>COUNTIFS($A:$A,A13,$B:$B,B13,$C:$C,C13,$D:$D,D13,$E:$E,E13,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J13" s="3">
+      <c r="J13" s="10">
         <f>F13+G13+H13-I13</f>
         <v/>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="K13" s="10" t="inlineStr">
         <is>
           <t>24-0721-0012</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="14">
         <f>COUNTIFS($A:$A,A14,$B:$B,B14,$C:$C,C14,$D:$D,D14,$E:$E,E14,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="14">
         <f>COUNTIFS($A:$A,A14,$B:$B,B14,$C:$C,C14,$D:$D,D14,$E:$E,E14,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="14">
         <f>COUNTIFS($A:$A,A14,$B:$B,B14,$C:$C,C14,$D:$D,D14,$E:$E,E14,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="14">
         <f>F14+G14+H14-I14</f>
         <v/>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="14" t="inlineStr">
         <is>
           <t>24-0721-0013</t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
+      <c r="L14" s="15" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="6">
         <f>COUNTIFS($A:$A,A15,$B:$B,B15,$C:$C,C15,$D:$D,D15,$E:$E,E15,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="6">
         <f>COUNTIFS($A:$A,A15,$B:$B,B15,$C:$C,C15,$D:$D,D15,$E:$E,E15,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="6">
         <f>COUNTIFS($A:$A,A15,$B:$B,B15,$C:$C,C15,$D:$D,D15,$E:$E,E15,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="J15" s="3">
+      <c r="J15" s="6">
         <f>F15+G15+H15-I15</f>
         <v/>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="K15" s="6" t="inlineStr">
         <is>
           <t>24-1102-0014</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="L15" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="10">
         <f>COUNTIFS($A:$A,A16,$B:$B,B16,$C:$C,C16,$D:$D,D16,$E:$E,E16,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="10">
         <f>COUNTIFS($A:$A,A16,$B:$B,B16,$C:$C,C16,$D:$D,D16,$E:$E,E16,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="10">
         <f>COUNTIFS($A:$A,A16,$B:$B,B16,$C:$C,C16,$D:$D,D16,$E:$E,E16,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J16" s="3">
+      <c r="J16" s="10">
         <f>F16+G16+H16-I16</f>
         <v/>
       </c>
-      <c r="K16" s="3" t="inlineStr">
+      <c r="K16" s="10" t="inlineStr">
         <is>
           <t>24-1102-0015</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="L16" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F17" s="3">
+      <c r="F17" s="10">
         <f>COUNTIFS($A:$A,A17,$B:$B,B17,$C:$C,C17,$D:$D,D17,$E:$E,E17,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="10">
         <f>COUNTIFS($A:$A,A17,$B:$B,B17,$C:$C,C17,$D:$D,D17,$E:$E,E17,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="10">
         <f>COUNTIFS($A:$A,A17,$B:$B,B17,$C:$C,C17,$D:$D,D17,$E:$E,E17,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J17" s="3">
+      <c r="J17" s="10">
         <f>F17+G17+H17-I17</f>
         <v/>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="K17" s="10" t="inlineStr">
         <is>
           <t>24-1102-0016</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="L17" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F18" s="3">
+      <c r="F18" s="10">
         <f>COUNTIFS($A:$A,A18,$B:$B,B18,$C:$C,C18,$D:$D,D18,$E:$E,E18,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="10">
         <f>COUNTIFS($A:$A,A18,$B:$B,B18,$C:$C,C18,$D:$D,D18,$E:$E,E18,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="10">
         <f>COUNTIFS($A:$A,A18,$B:$B,B18,$C:$C,C18,$D:$D,D18,$E:$E,E18,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J18" s="3">
+      <c r="J18" s="10">
         <f>F18+G18+H18-I18</f>
         <v/>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K18" s="10" t="inlineStr">
         <is>
           <t>24-1102-0017</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L18" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F19" s="3">
+      <c r="F19" s="10">
         <f>COUNTIFS($A:$A,A19,$B:$B,B19,$C:$C,C19,$D:$D,D19,$E:$E,E19,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="10">
         <f>COUNTIFS($A:$A,A19,$B:$B,B19,$C:$C,C19,$D:$D,D19,$E:$E,E19,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H19" s="3">
+      <c r="H19" s="10">
         <f>COUNTIFS($A:$A,A19,$B:$B,B19,$C:$C,C19,$D:$D,D19,$E:$E,E19,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="10">
         <f>F19+G19+H19-I19</f>
         <v/>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="K19" s="10" t="inlineStr">
         <is>
           <t>24-1102-0018</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="L19" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F20" s="3">
+      <c r="F20" s="10">
         <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="10">
         <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H20" s="3">
+      <c r="H20" s="10">
         <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="10">
         <f>F20+G20+H20-I20</f>
         <v/>
       </c>
-      <c r="K20" s="3" t="inlineStr">
+      <c r="K20" s="10" t="inlineStr">
         <is>
           <t>24-1102-0019</t>
         </is>
       </c>
-      <c r="L20" s="3" t="inlineStr">
+      <c r="L20" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="10">
         <f>COUNTIFS($A:$A,A21,$B:$B,B21,$C:$C,C21,$D:$D,D21,$E:$E,E21,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="10">
         <f>COUNTIFS($A:$A,A21,$B:$B,B21,$C:$C,C21,$D:$D,D21,$E:$E,E21,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H21" s="3">
+      <c r="H21" s="10">
         <f>COUNTIFS($A:$A,A21,$B:$B,B21,$C:$C,C21,$D:$D,D21,$E:$E,E21,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J21" s="3">
+      <c r="J21" s="10">
         <f>F21+G21+H21-I21</f>
         <v/>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="K21" s="10" t="inlineStr">
         <is>
           <t>24-1102-0020</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="L21" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="14">
         <f>COUNTIFS($A:$A,A22,$B:$B,B22,$C:$C,C22,$D:$D,D22,$E:$E,E22,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="14">
         <f>COUNTIFS($A:$A,A22,$B:$B,B22,$C:$C,C22,$D:$D,D22,$E:$E,E22,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H22" s="3">
+      <c r="H22" s="14">
         <f>COUNTIFS($A:$A,A22,$B:$B,B22,$C:$C,C22,$D:$D,D22,$E:$E,E22,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="J22" s="3">
+      <c r="J22" s="14">
         <f>F22+G22+H22-I22</f>
         <v/>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K22" s="14" t="inlineStr">
         <is>
           <t>24-1102-0021</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L22" s="15" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="6">
         <f>COUNTIFS($A:$A,A23,$B:$B,B23,$C:$C,C23,$D:$D,D23,$E:$E,E23,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="6">
         <f>COUNTIFS($A:$A,A23,$B:$B,B23,$C:$C,C23,$D:$D,D23,$E:$E,E23,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="6">
         <f>COUNTIFS($A:$A,A23,$B:$B,B23,$C:$C,C23,$D:$D,D23,$E:$E,E23,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="J23" s="3">
+      <c r="J23" s="6">
         <f>F23+G23+H23-I23</f>
         <v/>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="K23" s="6" t="inlineStr">
         <is>
           <t>25-0210-0001</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="L23" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="10">
         <f>COUNTIFS($A:$A,A24,$B:$B,B24,$C:$C,C24,$D:$D,D24,$E:$E,E24,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="10">
         <f>COUNTIFS($A:$A,A24,$B:$B,B24,$C:$C,C24,$D:$D,D24,$E:$E,E24,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H24" s="3">
+      <c r="H24" s="10">
         <f>COUNTIFS($A:$A,A24,$B:$B,B24,$C:$C,C24,$D:$D,D24,$E:$E,E24,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J24" s="3">
+      <c r="J24" s="10">
         <f>F24+G24+H24-I24</f>
         <v/>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>25-0210-0002</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L24" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F25" s="3">
+      <c r="F25" s="10">
         <f>COUNTIFS($A:$A,A25,$B:$B,B25,$C:$C,C25,$D:$D,D25,$E:$E,E25,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="10">
         <f>COUNTIFS($A:$A,A25,$B:$B,B25,$C:$C,C25,$D:$D,D25,$E:$E,E25,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H25" s="3">
+      <c r="H25" s="10">
         <f>COUNTIFS($A:$A,A25,$B:$B,B25,$C:$C,C25,$D:$D,D25,$E:$E,E25,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J25" s="3">
+      <c r="J25" s="10">
         <f>F25+G25+H25-I25</f>
         <v/>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>25-0210-0003</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L25" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F26" s="3">
+      <c r="F26" s="10">
         <f>COUNTIFS($A:$A,A26,$B:$B,B26,$C:$C,C26,$D:$D,D26,$E:$E,E26,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="10">
         <f>COUNTIFS($A:$A,A26,$B:$B,B26,$C:$C,C26,$D:$D,D26,$E:$E,E26,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="10">
         <f>COUNTIFS($A:$A,A26,$B:$B,B26,$C:$C,C26,$D:$D,D26,$E:$E,E26,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J26" s="3">
+      <c r="J26" s="10">
         <f>F26+G26+H26-I26</f>
         <v/>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K26" s="10" t="inlineStr">
         <is>
           <t>25-0210-0004</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L26" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="9" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F27" s="3">
+      <c r="F27" s="10">
         <f>COUNTIFS($A:$A,A27,$B:$B,B27,$C:$C,C27,$D:$D,D27,$E:$E,E27,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="10">
         <f>COUNTIFS($A:$A,A27,$B:$B,B27,$C:$C,C27,$D:$D,D27,$E:$E,E27,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H27" s="3">
+      <c r="H27" s="10">
         <f>COUNTIFS($A:$A,A27,$B:$B,B27,$C:$C,C27,$D:$D,D27,$E:$E,E27,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J27" s="3">
+      <c r="J27" s="10">
         <f>F27+G27+H27-I27</f>
         <v/>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="K27" s="10" t="inlineStr">
         <is>
           <t>25-0210-0005</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="L27" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" s="9" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F28" s="3">
+      <c r="F28" s="10">
         <f>COUNTIFS($A:$A,A28,$B:$B,B28,$C:$C,C28,$D:$D,D28,$E:$E,E28,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="10">
         <f>COUNTIFS($A:$A,A28,$B:$B,B28,$C:$C,C28,$D:$D,D28,$E:$E,E28,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H28" s="3">
+      <c r="H28" s="10">
         <f>COUNTIFS($A:$A,A28,$B:$B,B28,$C:$C,C28,$D:$D,D28,$E:$E,E28,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J28" s="3">
+      <c r="J28" s="10">
         <f>F28+G28+H28-I28</f>
         <v/>
       </c>
-      <c r="K28" s="3" t="inlineStr">
+      <c r="K28" s="10" t="inlineStr">
         <is>
           <t>25-0210-0006</t>
         </is>
       </c>
-      <c r="L28" s="3" t="inlineStr">
+      <c r="L28" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F29" s="3">
+      <c r="F29" s="10">
         <f>COUNTIFS($A:$A,A29,$B:$B,B29,$C:$C,C29,$D:$D,D29,$E:$E,E29,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="10">
         <f>COUNTIFS($A:$A,A29,$B:$B,B29,$C:$C,C29,$D:$D,D29,$E:$E,E29,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="10">
         <f>COUNTIFS($A:$A,A29,$B:$B,B29,$C:$C,C29,$D:$D,D29,$E:$E,E29,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J29" s="3">
+      <c r="J29" s="10">
         <f>F29+G29+H29-I29</f>
         <v/>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="K29" s="10" t="inlineStr">
         <is>
           <t>25-0518-0007</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="L29" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F30" s="3">
+      <c r="F30" s="10">
         <f>COUNTIFS($A:$A,A30,$B:$B,B30,$C:$C,C30,$D:$D,D30,$E:$E,E30,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="10">
         <f>COUNTIFS($A:$A,A30,$B:$B,B30,$C:$C,C30,$D:$D,D30,$E:$E,E30,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H30" s="3">
+      <c r="H30" s="10">
         <f>COUNTIFS($A:$A,A30,$B:$B,B30,$C:$C,C30,$D:$D,D30,$E:$E,E30,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J30" s="3">
+      <c r="J30" s="10">
         <f>F30+G30+H30-I30</f>
         <v/>
       </c>
-      <c r="K30" s="3" t="inlineStr">
+      <c r="K30" s="10" t="inlineStr">
         <is>
           <t>25-0518-0008</t>
         </is>
       </c>
-      <c r="L30" s="3" t="inlineStr">
+      <c r="L30" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F31" s="3">
+      <c r="F31" s="10">
         <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G31" s="3">
+      <c r="G31" s="10">
         <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H31" s="3">
+      <c r="H31" s="10">
         <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="J31" s="3">
+      <c r="J31" s="10">
         <f>F31+G31+H31-I31</f>
         <v/>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="K31" s="10" t="inlineStr">
         <is>
           <t>25-0518-0009</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="L31" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="12" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="13" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="13" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="13" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F32" s="3">
+      <c r="F32" s="14">
         <f>COUNTIFS($A:$A,A32,$B:$B,B32,$C:$C,C32,$D:$D,D32,$E:$E,E32,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G32" s="3">
+      <c r="G32" s="14">
         <f>COUNTIFS($A:$A,A32,$B:$B,B32,$C:$C,C32,$D:$D,D32,$E:$E,E32,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H32" s="3">
+      <c r="H32" s="14">
         <f>COUNTIFS($A:$A,A32,$B:$B,B32,$C:$C,C32,$D:$D,D32,$E:$E,E32,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="14">
         <f>F32+G32+H32-I32</f>
         <v/>
       </c>
-      <c r="K32" s="3" t="inlineStr">
+      <c r="K32" s="14" t="inlineStr">
         <is>
           <t>25-0518-0010</t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
+      <c r="L32" s="15" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F33" s="3">
+      <c r="F33" s="6">
         <f>COUNTIFS($A:$A,A33,$B:$B,B33,$C:$C,C33,$D:$D,D33,$E:$E,E33,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G33" s="3">
+      <c r="G33" s="6">
         <f>COUNTIFS($A:$A,A33,$B:$B,B33,$C:$C,C33,$D:$D,D33,$E:$E,E33,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H33" s="3">
+      <c r="H33" s="6">
         <f>COUNTIFS($A:$A,A33,$B:$B,B33,$C:$C,C33,$D:$D,D33,$E:$E,E33,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="I33" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J33" s="3">
+      <c r="J33" s="6">
         <f>F33+G33+H33-I33</f>
         <v/>
       </c>
-      <c r="K33" s="3" t="inlineStr">
+      <c r="K33" s="6" t="inlineStr">
         <is>
           <t>25-0927-0011</t>
         </is>
       </c>
-      <c r="L33" s="3" t="inlineStr">
+      <c r="L33" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F34" s="3">
+      <c r="F34" s="10">
         <f>COUNTIFS($A:$A,A34,$B:$B,B34,$C:$C,C34,$D:$D,D34,$E:$E,E34,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G34" s="3">
+      <c r="G34" s="10">
         <f>COUNTIFS($A:$A,A34,$B:$B,B34,$C:$C,C34,$D:$D,D34,$E:$E,E34,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H34" s="3">
+      <c r="H34" s="10">
         <f>COUNTIFS($A:$A,A34,$B:$B,B34,$C:$C,C34,$D:$D,D34,$E:$E,E34,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J34" s="3">
+      <c r="J34" s="10">
         <f>F34+G34+H34-I34</f>
         <v/>
       </c>
-      <c r="K34" s="3" t="inlineStr">
+      <c r="K34" s="10" t="inlineStr">
         <is>
           <t>25-0927-0012</t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
+      <c r="L34" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F35" s="3">
+      <c r="F35" s="10">
         <f>COUNTIFS($A:$A,A35,$B:$B,B35,$C:$C,C35,$D:$D,D35,$E:$E,E35,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G35" s="3">
+      <c r="G35" s="10">
         <f>COUNTIFS($A:$A,A35,$B:$B,B35,$C:$C,C35,$D:$D,D35,$E:$E,E35,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H35" s="3">
+      <c r="H35" s="10">
         <f>COUNTIFS($A:$A,A35,$B:$B,B35,$C:$C,C35,$D:$D,D35,$E:$E,E35,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J35" s="3">
+      <c r="J35" s="10">
         <f>F35+G35+H35-I35</f>
         <v/>
       </c>
-      <c r="K35" s="3" t="inlineStr">
+      <c r="K35" s="10" t="inlineStr">
         <is>
           <t>25-0927-0013</t>
         </is>
       </c>
-      <c r="L35" s="3" t="inlineStr">
+      <c r="L35" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F36" s="3">
+      <c r="F36" s="10">
         <f>COUNTIFS($A:$A,A36,$B:$B,B36,$C:$C,C36,$D:$D,D36,$E:$E,E36,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G36" s="3">
+      <c r="G36" s="10">
         <f>COUNTIFS($A:$A,A36,$B:$B,B36,$C:$C,C36,$D:$D,D36,$E:$E,E36,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H36" s="3">
+      <c r="H36" s="10">
         <f>COUNTIFS($A:$A,A36,$B:$B,B36,$C:$C,C36,$D:$D,D36,$E:$E,E36,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J36" s="3">
+      <c r="J36" s="10">
         <f>F36+G36+H36-I36</f>
         <v/>
       </c>
-      <c r="K36" s="3" t="inlineStr">
+      <c r="K36" s="10" t="inlineStr">
         <is>
           <t>25-0927-0014</t>
         </is>
       </c>
-      <c r="L36" s="3" t="inlineStr">
+      <c r="L36" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F37" s="3">
+      <c r="F37" s="10">
         <f>COUNTIFS($A:$A,A37,$B:$B,B37,$C:$C,C37,$D:$D,D37,$E:$E,E37,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G37" s="3">
+      <c r="G37" s="10">
         <f>COUNTIFS($A:$A,A37,$B:$B,B37,$C:$C,C37,$D:$D,D37,$E:$E,E37,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H37" s="3">
+      <c r="H37" s="10">
         <f>COUNTIFS($A:$A,A37,$B:$B,B37,$C:$C,C37,$D:$D,D37,$E:$E,E37,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="I37" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J37" s="3">
+      <c r="J37" s="10">
         <f>F37+G37+H37-I37</f>
         <v/>
       </c>
-      <c r="K37" s="3" t="inlineStr">
+      <c r="K37" s="10" t="inlineStr">
         <is>
           <t>25-0927-0015</t>
         </is>
       </c>
-      <c r="L37" s="3" t="inlineStr">
+      <c r="L37" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F38" s="3">
+      <c r="F38" s="10">
         <f>COUNTIFS($A:$A,A38,$B:$B,B38,$C:$C,C38,$D:$D,D38,$E:$E,E38,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G38" s="3">
+      <c r="G38" s="10">
         <f>COUNTIFS($A:$A,A38,$B:$B,B38,$C:$C,C38,$D:$D,D38,$E:$E,E38,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H38" s="3">
+      <c r="H38" s="10">
         <f>COUNTIFS($A:$A,A38,$B:$B,B38,$C:$C,C38,$D:$D,D38,$E:$E,E38,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J38" s="3">
+      <c r="J38" s="10">
         <f>F38+G38+H38-I38</f>
         <v/>
       </c>
-      <c r="K38" s="3" t="inlineStr">
+      <c r="K38" s="10" t="inlineStr">
         <is>
           <t>25-0927-0016</t>
         </is>
       </c>
-      <c r="L38" s="3" t="inlineStr">
+      <c r="L38" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F39" s="3">
+      <c r="F39" s="10">
         <f>COUNTIFS($A:$A,A39,$B:$B,B39,$C:$C,C39,$D:$D,D39,$E:$E,E39,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G39" s="3">
+      <c r="G39" s="10">
         <f>COUNTIFS($A:$A,A39,$B:$B,B39,$C:$C,C39,$D:$D,D39,$E:$E,E39,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H39" s="3">
+      <c r="H39" s="10">
         <f>COUNTIFS($A:$A,A39,$B:$B,B39,$C:$C,C39,$D:$D,D39,$E:$E,E39,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J39" s="3">
+      <c r="J39" s="10">
         <f>F39+G39+H39-I39</f>
         <v/>
       </c>
-      <c r="K39" s="3" t="inlineStr">
+      <c r="K39" s="10" t="inlineStr">
         <is>
           <t>25-0927-0017</t>
         </is>
       </c>
-      <c r="L39" s="3" t="inlineStr">
+      <c r="L39" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F40" s="3">
+      <c r="F40" s="10">
         <f>COUNTIFS($A:$A,A40,$B:$B,B40,$C:$C,C40,$D:$D,D40,$E:$E,E40,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G40" s="3">
+      <c r="G40" s="10">
         <f>COUNTIFS($A:$A,A40,$B:$B,B40,$C:$C,C40,$D:$D,D40,$E:$E,E40,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H40" s="3">
+      <c r="H40" s="10">
         <f>COUNTIFS($A:$A,A40,$B:$B,B40,$C:$C,C40,$D:$D,D40,$E:$E,E40,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J40" s="3">
+      <c r="J40" s="10">
         <f>F40+G40+H40-I40</f>
         <v/>
       </c>
-      <c r="K40" s="3" t="inlineStr">
+      <c r="K40" s="10" t="inlineStr">
         <is>
           <t>25-0927-0018</t>
         </is>
       </c>
-      <c r="L40" s="3" t="inlineStr">
+      <c r="L40" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" s="9" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
       </c>
-      <c r="F41" s="3">
+      <c r="F41" s="10">
         <f>COUNTIFS($A:$A,A41,$B:$B,B41,$C:$C,C41,$D:$D,D41,$E:$E,E41,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G41" s="3">
+      <c r="G41" s="10">
         <f>COUNTIFS($A:$A,A41,$B:$B,B41,$C:$C,C41,$D:$D,D41,$E:$E,E41,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H41" s="3">
+      <c r="H41" s="10">
         <f>COUNTIFS($A:$A,A41,$B:$B,B41,$C:$C,C41,$D:$D,D41,$E:$E,E41,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J41" s="3">
+      <c r="J41" s="10">
         <f>F41+G41+H41-I41</f>
         <v/>
       </c>
-      <c r="K41" s="3" t="inlineStr">
+      <c r="K41" s="10" t="inlineStr">
         <is>
           <t>25-0927-0019</t>
         </is>
       </c>
-      <c r="L41" s="3" t="inlineStr">
+      <c r="L41" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>Granada</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" s="13" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" s="13" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="13" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
       </c>
-      <c r="F42" s="3">
+      <c r="F42" s="14">
         <f>COUNTIFS($A:$A,A42,$B:$B,B42,$C:$C,C42,$D:$D,D42,$E:$E,E42,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="14">
         <f>COUNTIFS($A:$A,A42,$B:$B,B42,$C:$C,C42,$D:$D,D42,$E:$E,E42,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H42" s="3">
+      <c r="H42" s="14">
         <f>COUNTIFS($A:$A,A42,$B:$B,B42,$C:$C,C42,$D:$D,D42,$E:$E,E42,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="J42" s="3">
+      <c r="J42" s="14">
         <f>F42+G42+H42-I42</f>
         <v/>
       </c>
-      <c r="K42" s="3" t="inlineStr">
+      <c r="K42" s="14" t="inlineStr">
         <is>
           <t>25-0927-0020</t>
         </is>
       </c>
-      <c r="L42" s="3" t="inlineStr">
+      <c r="L42" s="15" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>Malaga</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F43" s="3">
+      <c r="F43" s="6">
         <f>COUNTIFS($A:$A,A43,$B:$B,B43,$C:$C,C43,$D:$D,D43,$E:$E,E43,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="6">
         <f>COUNTIFS($A:$A,A43,$B:$B,B43,$C:$C,C43,$D:$D,D43,$E:$E,E43,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="6">
         <f>COUNTIFS($A:$A,A43,$B:$B,B43,$C:$C,C43,$D:$D,D43,$E:$E,E43,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I43" s="3" t="n">
+      <c r="I43" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="J43" s="3">
+      <c r="J43" s="6">
         <f>F43+G43+H43-I43</f>
         <v/>
       </c>
-      <c r="K43" s="3" t="inlineStr">
+      <c r="K43" s="6" t="inlineStr">
         <is>
           <t>25-1205-0021</t>
         </is>
       </c>
-      <c r="L43" s="3" t="inlineStr">
+      <c r="L43" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="8" t="inlineStr">
         <is>
           <t>Malaga</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="10">
         <f>COUNTIFS($A:$A,A44,$B:$B,B44,$C:$C,C44,$D:$D,D44,$E:$E,E44,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="10">
         <f>COUNTIFS($A:$A,A44,$B:$B,B44,$C:$C,C44,$D:$D,D44,$E:$E,E44,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="10">
         <f>COUNTIFS($A:$A,A44,$B:$B,B44,$C:$C,C44,$D:$D,D44,$E:$E,E44,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J44" s="3">
+      <c r="J44" s="10">
         <f>F44+G44+H44-I44</f>
         <v/>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K44" s="10" t="inlineStr">
         <is>
           <t>25-1205-0022</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="L44" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Malaga</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F45" s="3">
+      <c r="F45" s="10">
         <f>COUNTIFS($A:$A,A45,$B:$B,B45,$C:$C,C45,$D:$D,D45,$E:$E,E45,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="10">
         <f>COUNTIFS($A:$A,A45,$B:$B,B45,$C:$C,C45,$D:$D,D45,$E:$E,E45,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="10">
         <f>COUNTIFS($A:$A,A45,$B:$B,B45,$C:$C,C45,$D:$D,D45,$E:$E,E45,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="10">
         <f>F45+G45+H45-I45</f>
         <v/>
       </c>
-      <c r="K45" s="3" t="inlineStr">
+      <c r="K45" s="10" t="inlineStr">
         <is>
           <t>25-1205-0023</t>
         </is>
       </c>
-      <c r="L45" s="3" t="inlineStr">
+      <c r="L45" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" s="12" t="inlineStr">
         <is>
           <t>Malaga</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" s="13" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" s="13" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" s="13" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="F46" s="3">
+      <c r="F46" s="14">
         <f>COUNTIFS($A:$A,A46,$B:$B,B46,$C:$C,C46,$D:$D,D46,$E:$E,E46,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G46" s="3">
+      <c r="G46" s="14">
         <f>COUNTIFS($A:$A,A46,$B:$B,B46,$C:$C,C46,$D:$D,D46,$E:$E,E46,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H46" s="3">
+      <c r="H46" s="14">
         <f>COUNTIFS($A:$A,A46,$B:$B,B46,$C:$C,C46,$D:$D,D46,$E:$E,E46,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="J46" s="3">
+      <c r="J46" s="14">
         <f>F46+G46+H46-I46</f>
         <v/>
       </c>
-      <c r="K46" s="3" t="inlineStr">
+      <c r="K46" s="14" t="inlineStr">
         <is>
           <t>25-1205-0024</t>
         </is>
       </c>
-      <c r="L46" s="3" t="inlineStr">
+      <c r="L46" s="15" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F47" s="3">
+      <c r="F47" s="6">
         <f>COUNTIFS($A:$A,A47,$B:$B,B47,$C:$C,C47,$D:$D,D47,$E:$E,E47,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="6">
         <f>COUNTIFS($A:$A,A47,$B:$B,B47,$C:$C,C47,$D:$D,D47,$E:$E,E47,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H47" s="3">
+      <c r="H47" s="6">
         <f>COUNTIFS($A:$A,A47,$B:$B,B47,$C:$C,C47,$D:$D,D47,$E:$E,E47,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I47" s="3" t="n">
+      <c r="I47" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="6">
         <f>F47+G47+H47-I47</f>
         <v/>
       </c>
-      <c r="K47" s="3" t="inlineStr">
+      <c r="K47" s="6" t="inlineStr">
         <is>
           <t>26-0103-0001</t>
         </is>
       </c>
-      <c r="L47" s="3" t="inlineStr">
+      <c r="L47" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F48" s="3">
+      <c r="F48" s="10">
         <f>COUNTIFS($A:$A,A48,$B:$B,B48,$C:$C,C48,$D:$D,D48,$E:$E,E48,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G48" s="3">
+      <c r="G48" s="10">
         <f>COUNTIFS($A:$A,A48,$B:$B,B48,$C:$C,C48,$D:$D,D48,$E:$E,E48,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H48" s="3">
+      <c r="H48" s="10">
         <f>COUNTIFS($A:$A,A48,$B:$B,B48,$C:$C,C48,$D:$D,D48,$E:$E,E48,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="I48" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="10">
         <f>F48+G48+H48-I48</f>
         <v/>
       </c>
-      <c r="K48" s="3" t="inlineStr">
+      <c r="K48" s="10" t="inlineStr">
         <is>
           <t>26-0103-0002</t>
         </is>
       </c>
-      <c r="L48" s="3" t="inlineStr">
+      <c r="L48" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F49" s="3">
+      <c r="F49" s="10">
         <f>COUNTIFS($A:$A,A49,$B:$B,B49,$C:$C,C49,$D:$D,D49,$E:$E,E49,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G49" s="3">
+      <c r="G49" s="10">
         <f>COUNTIFS($A:$A,A49,$B:$B,B49,$C:$C,C49,$D:$D,D49,$E:$E,E49,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H49" s="3">
+      <c r="H49" s="10">
         <f>COUNTIFS($A:$A,A49,$B:$B,B49,$C:$C,C49,$D:$D,D49,$E:$E,E49,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I49" s="3" t="n">
+      <c r="I49" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J49" s="3">
+      <c r="J49" s="10">
         <f>F49+G49+H49-I49</f>
         <v/>
       </c>
-      <c r="K49" s="3" t="inlineStr">
+      <c r="K49" s="10" t="inlineStr">
         <is>
           <t>26-0103-0003</t>
         </is>
       </c>
-      <c r="L49" s="3" t="inlineStr">
+      <c r="L49" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F50" s="3">
+      <c r="F50" s="10">
         <f>COUNTIFS($A:$A,A50,$B:$B,B50,$C:$C,C50,$D:$D,D50,$E:$E,E50,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G50" s="3">
+      <c r="G50" s="10">
         <f>COUNTIFS($A:$A,A50,$B:$B,B50,$C:$C,C50,$D:$D,D50,$E:$E,E50,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H50" s="3">
+      <c r="H50" s="10">
         <f>COUNTIFS($A:$A,A50,$B:$B,B50,$C:$C,C50,$D:$D,D50,$E:$E,E50,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="I50" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J50" s="3">
+      <c r="J50" s="10">
         <f>F50+G50+H50-I50</f>
         <v/>
       </c>
-      <c r="K50" s="3" t="inlineStr">
+      <c r="K50" s="10" t="inlineStr">
         <is>
           <t>26-0103-0004</t>
         </is>
       </c>
-      <c r="L50" s="3" t="inlineStr">
+      <c r="L50" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F51" s="3">
+      <c r="F51" s="10">
         <f>COUNTIFS($A:$A,A51,$B:$B,B51,$C:$C,C51,$D:$D,D51,$E:$E,E51,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G51" s="3">
+      <c r="G51" s="10">
         <f>COUNTIFS($A:$A,A51,$B:$B,B51,$C:$C,C51,$D:$D,D51,$E:$E,E51,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H51" s="3">
+      <c r="H51" s="10">
         <f>COUNTIFS($A:$A,A51,$B:$B,B51,$C:$C,C51,$D:$D,D51,$E:$E,E51,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I51" s="3" t="n">
+      <c r="I51" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J51" s="10">
         <f>F51+G51+H51-I51</f>
         <v/>
       </c>
-      <c r="K51" s="3" t="inlineStr">
+      <c r="K51" s="10" t="inlineStr">
         <is>
           <t>26-0103-0005</t>
         </is>
       </c>
-      <c r="L51" s="3" t="inlineStr">
+      <c r="L51" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="10">
         <f>COUNTIFS($A:$A,A52,$B:$B,B52,$C:$C,C52,$D:$D,D52,$E:$E,E52,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G52" s="3">
+      <c r="G52" s="10">
         <f>COUNTIFS($A:$A,A52,$B:$B,B52,$C:$C,C52,$D:$D,D52,$E:$E,E52,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H52" s="3">
+      <c r="H52" s="10">
         <f>COUNTIFS($A:$A,A52,$B:$B,B52,$C:$C,C52,$D:$D,D52,$E:$E,E52,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I52" s="3" t="n">
+      <c r="I52" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J52" s="3">
+      <c r="J52" s="10">
         <f>F52+G52+H52-I52</f>
         <v/>
       </c>
-      <c r="K52" s="3" t="inlineStr">
+      <c r="K52" s="10" t="inlineStr">
         <is>
           <t>26-0103-0006</t>
         </is>
       </c>
-      <c r="L52" s="3" t="inlineStr">
+      <c r="L52" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F53" s="3">
+      <c r="F53" s="10">
         <f>COUNTIFS($A:$A,A53,$B:$B,B53,$C:$C,C53,$D:$D,D53,$E:$E,E53,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G53" s="3">
+      <c r="G53" s="10">
         <f>COUNTIFS($A:$A,A53,$B:$B,B53,$C:$C,C53,$D:$D,D53,$E:$E,E53,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H53" s="3">
+      <c r="H53" s="10">
         <f>COUNTIFS($A:$A,A53,$B:$B,B53,$C:$C,C53,$D:$D,D53,$E:$E,E53,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I53" s="3" t="n">
+      <c r="I53" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J53" s="3">
+      <c r="J53" s="10">
         <f>F53+G53+H53-I53</f>
         <v/>
       </c>
-      <c r="K53" s="3" t="inlineStr">
+      <c r="K53" s="10" t="inlineStr">
         <is>
           <t>26-0103-0007</t>
         </is>
       </c>
-      <c r="L53" s="3" t="inlineStr">
+      <c r="L53" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" s="9" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F54" s="3">
+      <c r="F54" s="10">
         <f>COUNTIFS($A:$A,A54,$B:$B,B54,$C:$C,C54,$D:$D,D54,$E:$E,E54,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G54" s="3">
+      <c r="G54" s="10">
         <f>COUNTIFS($A:$A,A54,$B:$B,B54,$C:$C,C54,$D:$D,D54,$E:$E,E54,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H54" s="3">
+      <c r="H54" s="10">
         <f>COUNTIFS($A:$A,A54,$B:$B,B54,$C:$C,C54,$D:$D,D54,$E:$E,E54,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I54" s="3" t="n">
+      <c r="I54" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J54" s="3">
+      <c r="J54" s="10">
         <f>F54+G54+H54-I54</f>
         <v/>
       </c>
-      <c r="K54" s="3" t="inlineStr">
+      <c r="K54" s="10" t="inlineStr">
         <is>
           <t>26-0103-0008</t>
         </is>
       </c>
-      <c r="L54" s="3" t="inlineStr">
+      <c r="L54" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" s="13" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" s="13" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" s="13" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
       </c>
-      <c r="F55" s="3">
+      <c r="F55" s="14">
         <f>COUNTIFS($A:$A,A55,$B:$B,B55,$C:$C,C55,$D:$D,D55,$E:$E,E55,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G55" s="3">
+      <c r="G55" s="14">
         <f>COUNTIFS($A:$A,A55,$B:$B,B55,$C:$C,C55,$D:$D,D55,$E:$E,E55,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H55" s="3">
+      <c r="H55" s="14">
         <f>COUNTIFS($A:$A,A55,$B:$B,B55,$C:$C,C55,$D:$D,D55,$E:$E,E55,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I55" s="3" t="n">
+      <c r="I55" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="J55" s="3">
+      <c r="J55" s="14">
         <f>F55+G55+H55-I55</f>
         <v/>
       </c>
-      <c r="K55" s="3" t="inlineStr">
+      <c r="K55" s="14" t="inlineStr">
         <is>
           <t>26-0415-0009</t>
         </is>
       </c>
-      <c r="L55" s="3" t="inlineStr">
+      <c r="L55" s="15" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:L55">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>=$L2="In Stock"</formula>
+  <conditionalFormatting sqref="J2:J55">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
+      <formula>0</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>=$L2="Pre-Sale"</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L55">
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
+      <formula>"In Stock"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>=$L2="In Production"</formula>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="6">
+      <formula>"Pre-Sale"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="7">
+      <formula>"In Production"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" dxfId="8">
       <formula>=LEFT($L2,9)="Allocated"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/inventory_master.xlsx
+++ b/inventory_master.xlsx
@@ -191,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -238,6 +238,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -713,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L55"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -792,113 +795,58 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="16" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="16" customHeight="1"/>
+    <row r="3" ht="16" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Left Inswing</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F2" s="6">
-        <f>COUNTIFS($A:$A,A2,$B:$B,B2,$C:$C,C2,$D:$D,D2,$E:$E,E2,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G2" s="6">
-        <f>COUNTIFS($A:$A,A2,$B:$B,B2,$C:$C,C2,$D:$D,D2,$E:$E,E2,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H2" s="6">
-        <f>COUNTIFS($A:$A,A2,$B:$B,B2,$C:$C,C2,$D:$D,D2,$E:$E,E2,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I2" s="6" t="n">
+      <c r="F3" s="6">
+        <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"In Stock")</f>
+        <v/>
+      </c>
+      <c r="G3" s="6">
+        <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"In Production")</f>
+        <v/>
+      </c>
+      <c r="H3" s="6">
+        <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"Pre-Sale")</f>
+        <v/>
+      </c>
+      <c r="I3" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="J2" s="6">
-        <f>F2+G2+H2-I2</f>
-        <v/>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="J3" s="6">
+        <f>F3+G3+H3-I3</f>
+        <v/>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>24-0315-0001</t>
         </is>
       </c>
-      <c r="L2" s="7" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F3" s="10">
-        <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G3" s="10">
-        <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H3" s="10">
-        <f>COUNTIFS($A:$A,A3,$B:$B,B3,$C:$C,C3,$D:$D,D3,$E:$E,E3,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I3" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J3" s="10">
-        <f>F3+G3+H3-I3</f>
-        <v/>
-      </c>
-      <c r="K3" s="10" t="inlineStr">
-        <is>
-          <t>24-0315-0002</t>
-        </is>
-      </c>
-      <c r="L3" s="11" t="inlineStr">
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -930,28 +878,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F4" s="10">
-        <f>COUNTIFS($A:$A,A4,$B:$B,B4,$C:$C,C4,$D:$D,D4,$E:$E,E4,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G4" s="10">
-        <f>COUNTIFS($A:$A,A4,$B:$B,B4,$C:$C,C4,$D:$D,D4,$E:$E,E4,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H4" s="10">
-        <f>COUNTIFS($A:$A,A4,$B:$B,B4,$C:$C,C4,$D:$D,D4,$E:$E,E4,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
       <c r="I4" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J4" s="10">
-        <f>F4+G4+H4-I4</f>
-        <v/>
-      </c>
+      <c r="J4" s="10" t="n"/>
       <c r="K4" s="10" t="inlineStr">
         <is>
-          <t>24-0315-0003</t>
+          <t>24-0315-0002</t>
         </is>
       </c>
       <c r="L4" s="11" t="inlineStr">
@@ -986,28 +922,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F5" s="10">
-        <f>COUNTIFS($A:$A,A5,$B:$B,B5,$C:$C,C5,$D:$D,D5,$E:$E,E5,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G5" s="10">
-        <f>COUNTIFS($A:$A,A5,$B:$B,B5,$C:$C,C5,$D:$D,D5,$E:$E,E5,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H5" s="10">
-        <f>COUNTIFS($A:$A,A5,$B:$B,B5,$C:$C,C5,$D:$D,D5,$E:$E,E5,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
       <c r="I5" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="J5" s="10">
-        <f>F5+G5+H5-I5</f>
-        <v/>
-      </c>
+      <c r="J5" s="10" t="n"/>
       <c r="K5" s="10" t="inlineStr">
         <is>
-          <t>24-0315-0004</t>
+          <t>24-0315-0003</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
@@ -1024,7 +948,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -1034,7 +958,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -1042,28 +966,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F6" s="10">
-        <f>COUNTIFS($A:$A,A6,$B:$B,B6,$C:$C,C6,$D:$D,D6,$E:$E,E6,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G6" s="10">
-        <f>COUNTIFS($A:$A,A6,$B:$B,B6,$C:$C,C6,$D:$D,D6,$E:$E,E6,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H6" s="10">
-        <f>COUNTIFS($A:$A,A6,$B:$B,B6,$C:$C,C6,$D:$D,D6,$E:$E,E6,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" s="10">
-        <f>F6+G6+H6-I6</f>
-        <v/>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J6" s="10" t="n"/>
       <c r="K6" s="10" t="inlineStr">
         <is>
-          <t>24-0315-0005</t>
+          <t>24-0315-0004</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
@@ -1073,60 +985,18 @@
       </c>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F7" s="10">
-        <f>COUNTIFS($A:$A,A7,$B:$B,B7,$C:$C,C7,$D:$D,D7,$E:$E,E7,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G7" s="10">
-        <f>COUNTIFS($A:$A,A7,$B:$B,B7,$C:$C,C7,$D:$D,D7,$E:$E,E7,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H7" s="10">
-        <f>COUNTIFS($A:$A,A7,$B:$B,B7,$C:$C,C7,$D:$D,D7,$E:$E,E7,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I7" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J7" s="10">
-        <f>F7+G7+H7-I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>24-0315-0006</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="18" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -1175,7 +1045,7 @@
       </c>
       <c r="K8" s="10" t="inlineStr">
         <is>
-          <t>24-0315-0007</t>
+          <t>24-0315-0005</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
@@ -1210,28 +1080,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F9" s="10">
-        <f>COUNTIFS($A:$A,A9,$B:$B,B9,$C:$C,C9,$D:$D,D9,$E:$E,E9,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G9" s="10">
-        <f>COUNTIFS($A:$A,A9,$B:$B,B9,$C:$C,C9,$D:$D,D9,$E:$E,E9,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H9" s="10">
-        <f>COUNTIFS($A:$A,A9,$B:$B,B9,$C:$C,C9,$D:$D,D9,$E:$E,E9,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F9" s="10" t="n"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J9" s="10">
-        <f>F9+G9+H9-I9</f>
-        <v/>
-      </c>
+      <c r="J9" s="10" t="n"/>
       <c r="K9" s="10" t="inlineStr">
         <is>
-          <t>24-0315-0008</t>
+          <t>24-0315-0006</t>
         </is>
       </c>
       <c r="L9" s="11" t="inlineStr">
@@ -1266,28 +1124,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F10" s="10">
-        <f>COUNTIFS($A:$A,A10,$B:$B,B10,$C:$C,C10,$D:$D,D10,$E:$E,E10,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G10" s="10">
-        <f>COUNTIFS($A:$A,A10,$B:$B,B10,$C:$C,C10,$D:$D,D10,$E:$E,E10,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H10" s="10">
-        <f>COUNTIFS($A:$A,A10,$B:$B,B10,$C:$C,C10,$D:$D,D10,$E:$E,E10,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J10" s="10">
-        <f>F10+G10+H10-I10</f>
-        <v/>
-      </c>
+      <c r="J10" s="10" t="n"/>
       <c r="K10" s="10" t="inlineStr">
         <is>
-          <t>24-0315-0009</t>
+          <t>24-0315-0007</t>
         </is>
       </c>
       <c r="L10" s="11" t="inlineStr">
@@ -1322,28 +1168,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F11" s="10">
-        <f>COUNTIFS($A:$A,A11,$B:$B,B11,$C:$C,C11,$D:$D,D11,$E:$E,E11,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G11" s="10">
-        <f>COUNTIFS($A:$A,A11,$B:$B,B11,$C:$C,C11,$D:$D,D11,$E:$E,E11,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H11" s="10">
-        <f>COUNTIFS($A:$A,A11,$B:$B,B11,$C:$C,C11,$D:$D,D11,$E:$E,E11,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F11" s="10" t="n"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J11" s="10">
-        <f>F11+G11+H11-I11</f>
-        <v/>
-      </c>
+      <c r="J11" s="10" t="n"/>
       <c r="K11" s="10" t="inlineStr">
         <is>
-          <t>24-0315-0010</t>
+          <t>24-0315-0008</t>
         </is>
       </c>
       <c r="L11" s="11" t="inlineStr">
@@ -1378,28 +1212,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F12" s="10">
-        <f>COUNTIFS($A:$A,A12,$B:$B,B12,$C:$C,C12,$D:$D,D12,$E:$E,E12,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G12" s="10">
-        <f>COUNTIFS($A:$A,A12,$B:$B,B12,$C:$C,C12,$D:$D,D12,$E:$E,E12,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H12" s="10">
-        <f>COUNTIFS($A:$A,A12,$B:$B,B12,$C:$C,C12,$D:$D,D12,$E:$E,E12,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F12" s="10" t="n"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J12" s="10">
-        <f>F12+G12+H12-I12</f>
-        <v/>
-      </c>
+      <c r="J12" s="10" t="n"/>
       <c r="K12" s="10" t="inlineStr">
         <is>
-          <t>24-0315-0011</t>
+          <t>24-0315-0009</t>
         </is>
       </c>
       <c r="L12" s="11" t="inlineStr">
@@ -1416,46 +1238,34 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>36" x 96"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Oil-Rubbed Bronze</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
         <is>
-          <t>Right Outswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F13" s="10">
-        <f>COUNTIFS($A:$A,A13,$B:$B,B13,$C:$C,C13,$D:$D,D13,$E:$E,E13,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G13" s="10">
-        <f>COUNTIFS($A:$A,A13,$B:$B,B13,$C:$C,C13,$D:$D,D13,$E:$E,E13,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H13" s="10">
-        <f>COUNTIFS($A:$A,A13,$B:$B,B13,$C:$C,C13,$D:$D,D13,$E:$E,E13,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" s="10">
-        <f>F13+G13+H13-I13</f>
-        <v/>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J13" s="10" t="n"/>
       <c r="K13" s="10" t="inlineStr">
         <is>
-          <t>24-0721-0012</t>
+          <t>24-0315-0010</t>
         </is>
       </c>
       <c r="L13" s="11" t="inlineStr">
@@ -1465,141 +1275,87 @@
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Valencia</t>
         </is>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Right Outswing</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F14" s="14">
-        <f>COUNTIFS($A:$A,A14,$B:$B,B14,$C:$C,C14,$D:$D,D14,$E:$E,E14,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
-        <f>COUNTIFS($A:$A,A14,$B:$B,B14,$C:$C,C14,$D:$D,D14,$E:$E,E14,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H14" s="14">
-        <f>COUNTIFS($A:$A,A14,$B:$B,B14,$C:$C,C14,$D:$D,D14,$E:$E,E14,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I14" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="14">
-        <f>F14+G14+H14-I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="14" t="inlineStr">
-        <is>
-          <t>24-0721-0013</t>
-        </is>
-      </c>
-      <c r="L14" s="15" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="n"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" s="10" t="n"/>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>24-0315-0011</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F15" s="6">
-        <f>COUNTIFS($A:$A,A15,$B:$B,B15,$C:$C,C15,$D:$D,D15,$E:$E,E15,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G15" s="6">
-        <f>COUNTIFS($A:$A,A15,$B:$B,B15,$C:$C,C15,$D:$D,D15,$E:$E,E15,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H15" s="6">
-        <f>COUNTIFS($A:$A,A15,$B:$B,B15,$C:$C,C15,$D:$D,D15,$E:$E,E15,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" s="6">
-        <f>F15+G15+H15-I15</f>
-        <v/>
-      </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>24-1102-0014</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="17" t="n"/>
+      <c r="H15" s="17" t="n"/>
+      <c r="I15" s="17" t="n"/>
+      <c r="J15" s="17" t="n"/>
+      <c r="K15" s="17" t="n"/>
+      <c r="L15" s="18" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 96"</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>Brushed Nickel</t>
+          <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Right Outswing</t>
         </is>
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Frosted</t>
         </is>
       </c>
       <c r="F16" s="10">
@@ -1615,7 +1371,7 @@
         <v/>
       </c>
       <c r="I16" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J16" s="10">
         <f>F16+G16+H16-I16</f>
@@ -1623,7 +1379,7 @@
       </c>
       <c r="K16" s="10" t="inlineStr">
         <is>
-          <t>24-1102-0015</t>
+          <t>24-0721-0012</t>
         </is>
       </c>
       <c r="L16" s="11" t="inlineStr">
@@ -1633,224 +1389,128 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Oil-Rubbed Bronze</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Right Outswing</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n"/>
+      <c r="G17" s="14" t="n"/>
+      <c r="H17" s="14" t="n"/>
+      <c r="I17" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J17" s="14" t="n"/>
+      <c r="K17" s="14" t="inlineStr">
+        <is>
+          <t>24-0721-0013</t>
+        </is>
+      </c>
+      <c r="L17" s="15" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="17" t="n"/>
+      <c r="H18" s="17" t="n"/>
+      <c r="I18" s="17" t="n"/>
+      <c r="J18" s="17" t="n"/>
+      <c r="K18" s="17" t="n"/>
+      <c r="L18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="17" t="n"/>
+      <c r="H19" s="17" t="n"/>
+      <c r="I19" s="17" t="n"/>
+      <c r="J19" s="17" t="n"/>
+      <c r="K19" s="17" t="n"/>
+      <c r="L19" s="17" t="n"/>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B17" s="9" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
       </c>
-      <c r="F17" s="10">
-        <f>COUNTIFS($A:$A,A17,$B:$B,B17,$C:$C,C17,$D:$D,D17,$E:$E,E17,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G17" s="10">
-        <f>COUNTIFS($A:$A,A17,$B:$B,B17,$C:$C,C17,$D:$D,D17,$E:$E,E17,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H17" s="10">
-        <f>COUNTIFS($A:$A,A17,$B:$B,B17,$C:$C,C17,$D:$D,D17,$E:$E,E17,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I17" s="10" t="n">
+      <c r="F20" s="6">
+        <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"In Stock")</f>
+        <v/>
+      </c>
+      <c r="G20" s="6">
+        <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"In Production")</f>
+        <v/>
+      </c>
+      <c r="H20" s="6">
+        <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"Pre-Sale")</f>
+        <v/>
+      </c>
+      <c r="I20" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="J17" s="10">
-        <f>F17+G17+H17-I17</f>
-        <v/>
-      </c>
-      <c r="K17" s="10" t="inlineStr">
-        <is>
-          <t>24-1102-0016</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F18" s="10">
-        <f>COUNTIFS($A:$A,A18,$B:$B,B18,$C:$C,C18,$D:$D,D18,$E:$E,E18,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G18" s="10">
-        <f>COUNTIFS($A:$A,A18,$B:$B,B18,$C:$C,C18,$D:$D,D18,$E:$E,E18,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H18" s="10">
-        <f>COUNTIFS($A:$A,A18,$B:$B,B18,$C:$C,C18,$D:$D,D18,$E:$E,E18,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="10">
-        <f>F18+G18+H18-I18</f>
-        <v/>
-      </c>
-      <c r="K18" s="10" t="inlineStr">
-        <is>
-          <t>24-1102-0017</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E19" s="9" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F19" s="10">
-        <f>COUNTIFS($A:$A,A19,$B:$B,B19,$C:$C,C19,$D:$D,D19,$E:$E,E19,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G19" s="10">
-        <f>COUNTIFS($A:$A,A19,$B:$B,B19,$C:$C,C19,$D:$D,D19,$E:$E,E19,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H19" s="10">
-        <f>COUNTIFS($A:$A,A19,$B:$B,B19,$C:$C,C19,$D:$D,D19,$E:$E,E19,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="10">
-        <f>F19+G19+H19-I19</f>
-        <v/>
-      </c>
-      <c r="K19" s="10" t="inlineStr">
-        <is>
-          <t>24-1102-0018</t>
-        </is>
-      </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F20" s="10">
-        <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G20" s="10">
-        <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H20" s="10">
-        <f>COUNTIFS($A:$A,A20,$B:$B,B20,$C:$C,C20,$D:$D,D20,$E:$E,E20,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J20" s="10">
+      <c r="J20" s="6">
         <f>F20+G20+H20-I20</f>
         <v/>
       </c>
-      <c r="K20" s="10" t="inlineStr">
-        <is>
-          <t>24-1102-0019</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>24-1102-0014</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -1864,46 +1524,34 @@
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F21" s="10">
-        <f>COUNTIFS($A:$A,A21,$B:$B,B21,$C:$C,C21,$D:$D,D21,$E:$E,E21,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G21" s="10">
-        <f>COUNTIFS($A:$A,A21,$B:$B,B21,$C:$C,C21,$D:$D,D21,$E:$E,E21,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H21" s="10">
-        <f>COUNTIFS($A:$A,A21,$B:$B,B21,$C:$C,C21,$D:$D,D21,$E:$E,E21,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="n"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J21" s="10">
-        <f>F21+G21+H21-I21</f>
-        <v/>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="J21" s="10" t="n"/>
       <c r="K21" s="10" t="inlineStr">
         <is>
-          <t>24-1102-0020</t>
+          <t>24-1102-0015</t>
         </is>
       </c>
       <c r="L21" s="11" t="inlineStr">
@@ -1913,112 +1561,88 @@
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F22" s="14">
-        <f>COUNTIFS($A:$A,A22,$B:$B,B22,$C:$C,C22,$D:$D,D22,$E:$E,E22,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G22" s="14">
-        <f>COUNTIFS($A:$A,A22,$B:$B,B22,$C:$C,C22,$D:$D,D22,$E:$E,E22,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H22" s="14">
-        <f>COUNTIFS($A:$A,A22,$B:$B,B22,$C:$C,C22,$D:$D,D22,$E:$E,E22,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I22" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="J22" s="14">
-        <f>F22+G22+H22-I22</f>
-        <v/>
-      </c>
-      <c r="K22" s="14" t="inlineStr">
-        <is>
-          <t>24-1102-0021</t>
-        </is>
-      </c>
-      <c r="L22" s="15" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="n"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J22" s="10" t="n"/>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>24-1102-0016</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Cordova</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F23" s="6">
-        <f>COUNTIFS($A:$A,A23,$B:$B,B23,$C:$C,C23,$D:$D,D23,$E:$E,E23,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G23" s="6">
-        <f>COUNTIFS($A:$A,A23,$B:$B,B23,$C:$C,C23,$D:$D,D23,$E:$E,E23,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H23" s="6">
-        <f>COUNTIFS($A:$A,A23,$B:$B,B23,$C:$C,C23,$D:$D,D23,$E:$E,E23,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I23" s="6" t="n">
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J23" s="6">
-        <f>F23+G23+H23-I23</f>
-        <v/>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>25-0210-0001</t>
-        </is>
-      </c>
-      <c r="L23" s="7" t="inlineStr">
+      <c r="J23" s="10" t="n"/>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>24-1102-0017</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -2027,7 +1651,7 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Cordova</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -2037,7 +1661,7 @@
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -2047,31 +1671,19 @@
       </c>
       <c r="E24" s="9" t="inlineStr">
         <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F24" s="10">
-        <f>COUNTIFS($A:$A,A24,$B:$B,B24,$C:$C,C24,$D:$D,D24,$E:$E,E24,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G24" s="10">
-        <f>COUNTIFS($A:$A,A24,$B:$B,B24,$C:$C,C24,$D:$D,D24,$E:$E,E24,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H24" s="10">
-        <f>COUNTIFS($A:$A,A24,$B:$B,B24,$C:$C,C24,$D:$D,D24,$E:$E,E24,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="n"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J24" s="10">
-        <f>F24+G24+H24-I24</f>
-        <v/>
-      </c>
+      <c r="J24" s="10" t="n"/>
       <c r="K24" s="10" t="inlineStr">
         <is>
-          <t>25-0210-0002</t>
+          <t>24-1102-0018</t>
         </is>
       </c>
       <c r="L24" s="11" t="inlineStr">
@@ -2081,85 +1693,43 @@
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Cordova</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C25" s="9" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D25" s="9" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>Frosted</t>
-        </is>
-      </c>
-      <c r="F25" s="10">
-        <f>COUNTIFS($A:$A,A25,$B:$B,B25,$C:$C,C25,$D:$D,D25,$E:$E,E25,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G25" s="10">
-        <f>COUNTIFS($A:$A,A25,$B:$B,B25,$C:$C,C25,$D:$D,D25,$E:$E,E25,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H25" s="10">
-        <f>COUNTIFS($A:$A,A25,$B:$B,B25,$C:$C,C25,$D:$D,D25,$E:$E,E25,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I25" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J25" s="10">
-        <f>F25+G25+H25-I25</f>
-        <v/>
-      </c>
-      <c r="K25" s="10" t="inlineStr">
-        <is>
-          <t>25-0210-0003</t>
-        </is>
-      </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="17" t="n"/>
+      <c r="H25" s="17" t="n"/>
+      <c r="I25" s="17" t="n"/>
+      <c r="J25" s="17" t="n"/>
+      <c r="K25" s="17" t="n"/>
+      <c r="L25" s="18" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Cordova</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E26" s="9" t="inlineStr">
         <is>
-          <t>Frosted</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F26" s="10">
@@ -2175,7 +1745,7 @@
         <v/>
       </c>
       <c r="I26" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J26" s="10">
         <f>F26+G26+H26-I26</f>
@@ -2183,7 +1753,7 @@
       </c>
       <c r="K26" s="10" t="inlineStr">
         <is>
-          <t>25-0210-0004</t>
+          <t>24-1102-0019</t>
         </is>
       </c>
       <c r="L26" s="11" t="inlineStr">
@@ -2195,390 +1765,258 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="n"/>
+      <c r="G27" s="10" t="n"/>
+      <c r="H27" s="10" t="n"/>
+      <c r="I27" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J27" s="10" t="n"/>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>24-1102-0020</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F28" s="14" t="n"/>
+      <c r="G28" s="14" t="n"/>
+      <c r="H28" s="14" t="n"/>
+      <c r="I28" s="14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" s="14" t="n"/>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>24-1102-0021</t>
+        </is>
+      </c>
+      <c r="L28" s="15" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="17" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="17" t="n"/>
+      <c r="H29" s="17" t="n"/>
+      <c r="I29" s="17" t="n"/>
+      <c r="J29" s="17" t="n"/>
+      <c r="K29" s="17" t="n"/>
+      <c r="L29" s="17" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="17" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="17" t="n"/>
+      <c r="H30" s="17" t="n"/>
+      <c r="I30" s="17" t="n"/>
+      <c r="J30" s="17" t="n"/>
+      <c r="K30" s="17" t="n"/>
+      <c r="L30" s="17" t="n"/>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B27" s="9" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F27" s="10">
-        <f>COUNTIFS($A:$A,A27,$B:$B,B27,$C:$C,C27,$D:$D,D27,$E:$E,E27,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G27" s="10">
-        <f>COUNTIFS($A:$A,A27,$B:$B,B27,$C:$C,C27,$D:$D,D27,$E:$E,E27,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H27" s="10">
-        <f>COUNTIFS($A:$A,A27,$B:$B,B27,$C:$C,C27,$D:$D,D27,$E:$E,E27,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I27" s="10" t="n">
+      <c r="F31" s="6">
+        <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"In Stock")</f>
+        <v/>
+      </c>
+      <c r="G31" s="6">
+        <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"In Production")</f>
+        <v/>
+      </c>
+      <c r="H31" s="6">
+        <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"Pre-Sale")</f>
+        <v/>
+      </c>
+      <c r="I31" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="J27" s="10">
-        <f>F27+G27+H27-I27</f>
-        <v/>
-      </c>
-      <c r="K27" s="10" t="inlineStr">
-        <is>
-          <t>25-0210-0005</t>
-        </is>
-      </c>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="J31" s="6">
+        <f>F31+G31+H31-I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>25-0210-0001</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
       </c>
-      <c r="F28" s="10">
-        <f>COUNTIFS($A:$A,A28,$B:$B,B28,$C:$C,C28,$D:$D,D28,$E:$E,E28,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G28" s="10">
-        <f>COUNTIFS($A:$A,A28,$B:$B,B28,$C:$C,C28,$D:$D,D28,$E:$E,E28,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H28" s="10">
-        <f>COUNTIFS($A:$A,A28,$B:$B,B28,$C:$C,C28,$D:$D,D28,$E:$E,E28,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I28" s="10" t="n">
+      <c r="F32" s="10" t="n"/>
+      <c r="G32" s="10" t="n"/>
+      <c r="H32" s="10" t="n"/>
+      <c r="I32" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J28" s="10">
-        <f>F28+G28+H28-I28</f>
-        <v/>
-      </c>
-      <c r="K28" s="10" t="inlineStr">
-        <is>
-          <t>25-0210-0006</t>
-        </is>
-      </c>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="J32" s="10" t="n"/>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>25-0210-0002</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
         <is>
           <t>Cordova</t>
         </is>
       </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E29" s="9" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F29" s="10">
-        <f>COUNTIFS($A:$A,A29,$B:$B,B29,$C:$C,C29,$D:$D,D29,$E:$E,E29,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G29" s="10">
-        <f>COUNTIFS($A:$A,A29,$B:$B,B29,$C:$C,C29,$D:$D,D29,$E:$E,E29,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H29" s="10">
-        <f>COUNTIFS($A:$A,A29,$B:$B,B29,$C:$C,C29,$D:$D,D29,$E:$E,E29,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I29" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J29" s="10">
-        <f>F29+G29+H29-I29</f>
-        <v/>
-      </c>
-      <c r="K29" s="10" t="inlineStr">
-        <is>
-          <t>25-0518-0007</t>
-        </is>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Cordova</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E30" s="9" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F30" s="10">
-        <f>COUNTIFS($A:$A,A30,$B:$B,B30,$C:$C,C30,$D:$D,D30,$E:$E,E30,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G30" s="10">
-        <f>COUNTIFS($A:$A,A30,$B:$B,B30,$C:$C,C30,$D:$D,D30,$E:$E,E30,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H30" s="10">
-        <f>COUNTIFS($A:$A,A30,$B:$B,B30,$C:$C,C30,$D:$D,D30,$E:$E,E30,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I30" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J30" s="10">
-        <f>F30+G30+H30-I30</f>
-        <v/>
-      </c>
-      <c r="K30" s="10" t="inlineStr">
-        <is>
-          <t>25-0518-0008</t>
-        </is>
-      </c>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Cordova</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Oil-Rubbed Bronze</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F31" s="10">
-        <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G31" s="10">
-        <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H31" s="10">
-        <f>COUNTIFS($A:$A,A31,$B:$B,B31,$C:$C,C31,$D:$D,D31,$E:$E,E31,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I31" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="J31" s="10">
-        <f>F31+G31+H31-I31</f>
-        <v/>
-      </c>
-      <c r="K31" s="10" t="inlineStr">
-        <is>
-          <t>25-0518-0009</t>
-        </is>
-      </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>Cordova</t>
-        </is>
-      </c>
-      <c r="B32" s="13" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>Right Outswing</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F32" s="14">
-        <f>COUNTIFS($A:$A,A32,$B:$B,B32,$C:$C,C32,$D:$D,D32,$E:$E,E32,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G32" s="14">
-        <f>COUNTIFS($A:$A,A32,$B:$B,B32,$C:$C,C32,$D:$D,D32,$E:$E,E32,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H32" s="14">
-        <f>COUNTIFS($A:$A,A32,$B:$B,B32,$C:$C,C32,$D:$D,D32,$E:$E,E32,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I32" s="14" t="n">
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="n"/>
+      <c r="G33" s="10" t="n"/>
+      <c r="H33" s="10" t="n"/>
+      <c r="I33" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="J32" s="14">
-        <f>F32+G32+H32-I32</f>
-        <v/>
-      </c>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>25-0518-0010</t>
-        </is>
-      </c>
-      <c r="L32" s="15" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F33" s="6">
-        <f>COUNTIFS($A:$A,A33,$B:$B,B33,$C:$C,C33,$D:$D,D33,$E:$E,E33,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G33" s="6">
-        <f>COUNTIFS($A:$A,A33,$B:$B,B33,$C:$C,C33,$D:$D,D33,$E:$E,E33,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H33" s="6">
-        <f>COUNTIFS($A:$A,A33,$B:$B,B33,$C:$C,C33,$D:$D,D33,$E:$E,E33,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I33" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J33" s="6">
-        <f>F33+G33+H33-I33</f>
-        <v/>
-      </c>
-      <c r="K33" s="6" t="inlineStr">
-        <is>
-          <t>25-0927-0011</t>
-        </is>
-      </c>
-      <c r="L33" s="7" t="inlineStr">
+      <c r="J33" s="10" t="n"/>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>25-0210-0003</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -2587,12 +2025,12 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cordova</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -2607,31 +2045,19 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F34" s="10">
-        <f>COUNTIFS($A:$A,A34,$B:$B,B34,$C:$C,C34,$D:$D,D34,$E:$E,E34,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G34" s="10">
-        <f>COUNTIFS($A:$A,A34,$B:$B,B34,$C:$C,C34,$D:$D,D34,$E:$E,E34,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H34" s="10">
-        <f>COUNTIFS($A:$A,A34,$B:$B,B34,$C:$C,C34,$D:$D,D34,$E:$E,E34,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="10" t="n"/>
+      <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J34" s="10">
-        <f>F34+G34+H34-I34</f>
-        <v/>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="J34" s="10" t="n"/>
       <c r="K34" s="10" t="inlineStr">
         <is>
-          <t>25-0927-0012</t>
+          <t>25-0210-0004</t>
         </is>
       </c>
       <c r="L34" s="11" t="inlineStr">
@@ -2643,12 +2069,12 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cordova</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C35" s="9" t="inlineStr">
@@ -2663,31 +2089,19 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F35" s="10">
-        <f>COUNTIFS($A:$A,A35,$B:$B,B35,$C:$C,C35,$D:$D,D35,$E:$E,E35,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G35" s="10">
-        <f>COUNTIFS($A:$A,A35,$B:$B,B35,$C:$C,C35,$D:$D,D35,$E:$E,E35,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H35" s="10">
-        <f>COUNTIFS($A:$A,A35,$B:$B,B35,$C:$C,C35,$D:$D,D35,$E:$E,E35,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="n"/>
+      <c r="G35" s="10" t="n"/>
+      <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J35" s="10">
-        <f>F35+G35+H35-I35</f>
-        <v/>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="J35" s="10" t="n"/>
       <c r="K35" s="10" t="inlineStr">
         <is>
-          <t>25-0927-0013</t>
+          <t>25-0210-0005</t>
         </is>
       </c>
       <c r="L35" s="11" t="inlineStr">
@@ -2699,12 +2113,12 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cordova</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>32" x 80"</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -2719,31 +2133,19 @@
       </c>
       <c r="E36" s="9" t="inlineStr">
         <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F36" s="10">
-        <f>COUNTIFS($A:$A,A36,$B:$B,B36,$C:$C,C36,$D:$D,D36,$E:$E,E36,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G36" s="10">
-        <f>COUNTIFS($A:$A,A36,$B:$B,B36,$C:$C,C36,$D:$D,D36,$E:$E,E36,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H36" s="10">
-        <f>COUNTIFS($A:$A,A36,$B:$B,B36,$C:$C,C36,$D:$D,D36,$E:$E,E36,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+          <t>Frosted</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="n"/>
+      <c r="G36" s="10" t="n"/>
+      <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J36" s="10">
-        <f>F36+G36+H36-I36</f>
-        <v/>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="J36" s="10" t="n"/>
       <c r="K36" s="10" t="inlineStr">
         <is>
-          <t>25-0927-0014</t>
+          <t>25-0210-0006</t>
         </is>
       </c>
       <c r="L36" s="11" t="inlineStr">
@@ -2753,65 +2155,23 @@
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>Right Inswing</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>Clear</t>
-        </is>
-      </c>
-      <c r="F37" s="10">
-        <f>COUNTIFS($A:$A,A37,$B:$B,B37,$C:$C,C37,$D:$D,D37,$E:$E,E37,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G37" s="10">
-        <f>COUNTIFS($A:$A,A37,$B:$B,B37,$C:$C,C37,$D:$D,D37,$E:$E,E37,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H37" s="10">
-        <f>COUNTIFS($A:$A,A37,$B:$B,B37,$C:$C,C37,$D:$D,D37,$E:$E,E37,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I37" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" s="10">
-        <f>F37+G37+H37-I37</f>
-        <v/>
-      </c>
-      <c r="K37" s="10" t="inlineStr">
-        <is>
-          <t>25-0927-0015</t>
-        </is>
-      </c>
-      <c r="L37" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="17" t="n"/>
+      <c r="H37" s="17" t="n"/>
+      <c r="I37" s="17" t="n"/>
+      <c r="J37" s="17" t="n"/>
+      <c r="K37" s="17" t="n"/>
+      <c r="L37" s="18" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cordova</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -2821,12 +2181,12 @@
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2847,7 +2207,7 @@
         <v/>
       </c>
       <c r="I38" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J38" s="10">
         <f>F38+G38+H38-I38</f>
@@ -2855,7 +2215,7 @@
       </c>
       <c r="K38" s="10" t="inlineStr">
         <is>
-          <t>25-0927-0016</t>
+          <t>25-0518-0007</t>
         </is>
       </c>
       <c r="L38" s="11" t="inlineStr">
@@ -2867,7 +2227,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cordova</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -2877,12 +2237,12 @@
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2890,28 +2250,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F39" s="10">
-        <f>COUNTIFS($A:$A,A39,$B:$B,B39,$C:$C,C39,$D:$D,D39,$E:$E,E39,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G39" s="10">
-        <f>COUNTIFS($A:$A,A39,$B:$B,B39,$C:$C,C39,$D:$D,D39,$E:$E,E39,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H39" s="10">
-        <f>COUNTIFS($A:$A,A39,$B:$B,B39,$C:$C,C39,$D:$D,D39,$E:$E,E39,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F39" s="10" t="n"/>
+      <c r="G39" s="10" t="n"/>
+      <c r="H39" s="10" t="n"/>
       <c r="I39" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J39" s="10">
-        <f>F39+G39+H39-I39</f>
-        <v/>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J39" s="10" t="n"/>
       <c r="K39" s="10" t="inlineStr">
         <is>
-          <t>25-0927-0017</t>
+          <t>25-0518-0008</t>
         </is>
       </c>
       <c r="L39" s="11" t="inlineStr">
@@ -2923,7 +2271,7 @@
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cordova</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -2933,12 +2281,12 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>Right Inswing</t>
+          <t>Left Inswing</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2946,28 +2294,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F40" s="10">
-        <f>COUNTIFS($A:$A,A40,$B:$B,B40,$C:$C,C40,$D:$D,D40,$E:$E,E40,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G40" s="10">
-        <f>COUNTIFS($A:$A,A40,$B:$B,B40,$C:$C,C40,$D:$D,D40,$E:$E,E40,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H40" s="10">
-        <f>COUNTIFS($A:$A,A40,$B:$B,B40,$C:$C,C40,$D:$D,D40,$E:$E,E40,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
       <c r="I40" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="J40" s="10">
-        <f>F40+G40+H40-I40</f>
-        <v/>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="J40" s="10" t="n"/>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>25-0927-0018</t>
+          <t>25-0518-0009</t>
         </is>
       </c>
       <c r="L40" s="11" t="inlineStr">
@@ -2977,65 +2313,23 @@
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t>Granada</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t>36" x 96"</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E41" s="9" t="inlineStr">
-        <is>
-          <t>Sidelite</t>
-        </is>
-      </c>
-      <c r="F41" s="10">
-        <f>COUNTIFS($A:$A,A41,$B:$B,B41,$C:$C,C41,$D:$D,D41,$E:$E,E41,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G41" s="10">
-        <f>COUNTIFS($A:$A,A41,$B:$B,B41,$C:$C,C41,$D:$D,D41,$E:$E,E41,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H41" s="10">
-        <f>COUNTIFS($A:$A,A41,$B:$B,B41,$C:$C,C41,$D:$D,D41,$E:$E,E41,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I41" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J41" s="10">
-        <f>F41+G41+H41-I41</f>
-        <v/>
-      </c>
-      <c r="K41" s="10" t="inlineStr">
-        <is>
-          <t>25-0927-0019</t>
-        </is>
-      </c>
-      <c r="L41" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="A41" s="16" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+      <c r="G41" s="17" t="n"/>
+      <c r="H41" s="17" t="n"/>
+      <c r="I41" s="17" t="n"/>
+      <c r="J41" s="17" t="n"/>
+      <c r="K41" s="17" t="n"/>
+      <c r="L41" s="18" t="n"/>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>Granada</t>
+          <t>Cordova</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
@@ -3045,17 +2339,17 @@
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Brushed Nickel</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Outswing</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>Sidelite</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="F42" s="14">
@@ -3071,7 +2365,7 @@
         <v/>
       </c>
       <c r="I42" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J42" s="14">
         <f>F42+G42+H42-I42</f>
@@ -3079,7 +2373,7 @@
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>25-0927-0020</t>
+          <t>25-0518-0010</t>
         </is>
       </c>
       <c r="L42" s="15" t="inlineStr">
@@ -3089,280 +2383,172 @@
       </c>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F43" s="6">
-        <f>COUNTIFS($A:$A,A43,$B:$B,B43,$C:$C,C43,$D:$D,D43,$E:$E,E43,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G43" s="6">
-        <f>COUNTIFS($A:$A,A43,$B:$B,B43,$C:$C,C43,$D:$D,D43,$E:$E,E43,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H43" s="6">
-        <f>COUNTIFS($A:$A,A43,$B:$B,B43,$C:$C,C43,$D:$D,D43,$E:$E,E43,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I43" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="J43" s="6">
-        <f>F43+G43+H43-I43</f>
-        <v/>
-      </c>
-      <c r="K43" s="6" t="inlineStr">
-        <is>
-          <t>25-1205-0021</t>
-        </is>
-      </c>
-      <c r="L43" s="7" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="A43" s="17" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+      <c r="G43" s="17" t="n"/>
+      <c r="H43" s="17" t="n"/>
+      <c r="I43" s="17" t="n"/>
+      <c r="J43" s="17" t="n"/>
+      <c r="K43" s="17" t="n"/>
+      <c r="L43" s="17" t="n"/>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F44" s="10">
-        <f>COUNTIFS($A:$A,A44,$B:$B,B44,$C:$C,C44,$D:$D,D44,$E:$E,E44,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G44" s="10">
-        <f>COUNTIFS($A:$A,A44,$B:$B,B44,$C:$C,C44,$D:$D,D44,$E:$E,E44,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H44" s="10">
-        <f>COUNTIFS($A:$A,A44,$B:$B,B44,$C:$C,C44,$D:$D,D44,$E:$E,E44,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I44" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J44" s="10">
-        <f>F44+G44+H44-I44</f>
-        <v/>
-      </c>
-      <c r="K44" s="10" t="inlineStr">
-        <is>
-          <t>25-1205-0022</t>
-        </is>
-      </c>
-      <c r="L44" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="A44" s="17" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+      <c r="G44" s="17" t="n"/>
+      <c r="H44" s="17" t="n"/>
+      <c r="I44" s="17" t="n"/>
+      <c r="J44" s="17" t="n"/>
+      <c r="K44" s="17" t="n"/>
+      <c r="L44" s="17" t="n"/>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E45" s="9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F45" s="10">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F45" s="6">
         <f>COUNTIFS($A:$A,A45,$B:$B,B45,$C:$C,C45,$D:$D,D45,$E:$E,E45,$L:$L,"In Stock")</f>
         <v/>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="6">
         <f>COUNTIFS($A:$A,A45,$B:$B,B45,$C:$C,C45,$D:$D,D45,$E:$E,E45,$L:$L,"In Production")</f>
         <v/>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="6">
         <f>COUNTIFS($A:$A,A45,$B:$B,B45,$C:$C,C45,$D:$D,D45,$E:$E,E45,$L:$L,"Pre-Sale")</f>
         <v/>
       </c>
-      <c r="I45" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="J45" s="10">
+      <c r="I45" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J45" s="6">
         <f>F45+G45+H45-I45</f>
         <v/>
       </c>
-      <c r="K45" s="10" t="inlineStr">
-        <is>
-          <t>25-1205-0023</t>
-        </is>
-      </c>
-      <c r="L45" s="11" t="inlineStr">
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>25-0927-0011</t>
+        </is>
+      </c>
+      <c r="L45" s="7" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C46" s="13" t="inlineStr">
-        <is>
-          <t>Brushed Nickel</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F46" s="14">
-        <f>COUNTIFS($A:$A,A46,$B:$B,B46,$C:$C,C46,$D:$D,D46,$E:$E,E46,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G46" s="14">
-        <f>COUNTIFS($A:$A,A46,$B:$B,B46,$C:$C,C46,$D:$D,D46,$E:$E,E46,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H46" s="14">
-        <f>COUNTIFS($A:$A,A46,$B:$B,B46,$C:$C,C46,$D:$D,D46,$E:$E,E46,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I46" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="J46" s="14">
-        <f>F46+G46+H46-I46</f>
-        <v/>
-      </c>
-      <c r="K46" s="14" t="inlineStr">
-        <is>
-          <t>25-1205-0024</t>
-        </is>
-      </c>
-      <c r="L46" s="15" t="inlineStr">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="n"/>
+      <c r="G46" s="10" t="n"/>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J46" s="10" t="n"/>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>25-0927-0012</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>Altea</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>32" x 80"</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Satin White</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
       </c>
-      <c r="F47" s="6">
-        <f>COUNTIFS($A:$A,A47,$B:$B,B47,$C:$C,C47,$D:$D,D47,$E:$E,E47,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G47" s="6">
-        <f>COUNTIFS($A:$A,A47,$B:$B,B47,$C:$C,C47,$D:$D,D47,$E:$E,E47,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H47" s="6">
-        <f>COUNTIFS($A:$A,A47,$B:$B,B47,$C:$C,C47,$D:$D,D47,$E:$E,E47,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="J47" s="6">
-        <f>F47+G47+H47-I47</f>
-        <v/>
-      </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>26-0103-0001</t>
-        </is>
-      </c>
-      <c r="L47" s="7" t="inlineStr">
+      <c r="F47" s="10" t="n"/>
+      <c r="G47" s="10" t="n"/>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J47" s="10" t="n"/>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>25-0927-0013</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
@@ -3371,17 +2557,17 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Altea</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -3394,28 +2580,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F48" s="10">
-        <f>COUNTIFS($A:$A,A48,$B:$B,B48,$C:$C,C48,$D:$D,D48,$E:$E,E48,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G48" s="10">
-        <f>COUNTIFS($A:$A,A48,$B:$B,B48,$C:$C,C48,$D:$D,D48,$E:$E,E48,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H48" s="10">
-        <f>COUNTIFS($A:$A,A48,$B:$B,B48,$C:$C,C48,$D:$D,D48,$E:$E,E48,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F48" s="10" t="n"/>
+      <c r="G48" s="10" t="n"/>
+      <c r="H48" s="10" t="n"/>
       <c r="I48" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J48" s="10">
-        <f>F48+G48+H48-I48</f>
-        <v/>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J48" s="10" t="n"/>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>26-0103-0002</t>
+          <t>25-0927-0014</t>
         </is>
       </c>
       <c r="L48" s="11" t="inlineStr">
@@ -3427,17 +2601,17 @@
     <row r="49" ht="16" customHeight="1">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Altea</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -3450,28 +2624,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F49" s="10">
-        <f>COUNTIFS($A:$A,A49,$B:$B,B49,$C:$C,C49,$D:$D,D49,$E:$E,E49,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G49" s="10">
-        <f>COUNTIFS($A:$A,A49,$B:$B,B49,$C:$C,C49,$D:$D,D49,$E:$E,E49,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H49" s="10">
-        <f>COUNTIFS($A:$A,A49,$B:$B,B49,$C:$C,C49,$D:$D,D49,$E:$E,E49,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F49" s="10" t="n"/>
+      <c r="G49" s="10" t="n"/>
+      <c r="H49" s="10" t="n"/>
       <c r="I49" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J49" s="10">
-        <f>F49+G49+H49-I49</f>
-        <v/>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J49" s="10" t="n"/>
       <c r="K49" s="10" t="inlineStr">
         <is>
-          <t>26-0103-0003</t>
+          <t>25-0927-0015</t>
         </is>
       </c>
       <c r="L49" s="11" t="inlineStr">
@@ -3483,17 +2645,17 @@
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Altea</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -3506,28 +2668,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F50" s="10">
-        <f>COUNTIFS($A:$A,A50,$B:$B,B50,$C:$C,C50,$D:$D,D50,$E:$E,E50,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G50" s="10">
-        <f>COUNTIFS($A:$A,A50,$B:$B,B50,$C:$C,C50,$D:$D,D50,$E:$E,E50,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H50" s="10">
-        <f>COUNTIFS($A:$A,A50,$B:$B,B50,$C:$C,C50,$D:$D,D50,$E:$E,E50,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F50" s="10" t="n"/>
+      <c r="G50" s="10" t="n"/>
+      <c r="H50" s="10" t="n"/>
       <c r="I50" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J50" s="10">
-        <f>F50+G50+H50-I50</f>
-        <v/>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J50" s="10" t="n"/>
       <c r="K50" s="10" t="inlineStr">
         <is>
-          <t>26-0103-0004</t>
+          <t>25-0927-0016</t>
         </is>
       </c>
       <c r="L50" s="11" t="inlineStr">
@@ -3539,17 +2689,17 @@
     <row r="51" ht="16" customHeight="1">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Altea</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>32" x 80"</t>
+          <t>36" x 80"</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Satin White</t>
+          <t>Matte Black</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -3562,28 +2712,16 @@
           <t>Clear</t>
         </is>
       </c>
-      <c r="F51" s="10">
-        <f>COUNTIFS($A:$A,A51,$B:$B,B51,$C:$C,C51,$D:$D,D51,$E:$E,E51,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G51" s="10">
-        <f>COUNTIFS($A:$A,A51,$B:$B,B51,$C:$C,C51,$D:$D,D51,$E:$E,E51,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H51" s="10">
-        <f>COUNTIFS($A:$A,A51,$B:$B,B51,$C:$C,C51,$D:$D,D51,$E:$E,E51,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+      <c r="F51" s="10" t="n"/>
+      <c r="G51" s="10" t="n"/>
+      <c r="H51" s="10" t="n"/>
       <c r="I51" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" s="10">
-        <f>F51+G51+H51-I51</f>
-        <v/>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J51" s="10" t="n"/>
       <c r="K51" s="10" t="inlineStr">
         <is>
-          <t>26-0103-0005</t>
+          <t>25-0927-0017</t>
         </is>
       </c>
       <c r="L51" s="11" t="inlineStr">
@@ -3595,7 +2733,7 @@
     <row r="52" ht="16" customHeight="1">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Altea</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -3610,36 +2748,24 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>Left Inswing</t>
+          <t>Right Inswing</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F52" s="10">
-        <f>COUNTIFS($A:$A,A52,$B:$B,B52,$C:$C,C52,$D:$D,D52,$E:$E,E52,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G52" s="10">
-        <f>COUNTIFS($A:$A,A52,$B:$B,B52,$C:$C,C52,$D:$D,D52,$E:$E,E52,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H52" s="10">
-        <f>COUNTIFS($A:$A,A52,$B:$B,B52,$C:$C,C52,$D:$D,D52,$E:$E,E52,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="n"/>
+      <c r="G52" s="10" t="n"/>
+      <c r="H52" s="10" t="n"/>
       <c r="I52" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" s="10">
-        <f>F52+G52+H52-I52</f>
-        <v/>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="J52" s="10" t="n"/>
       <c r="K52" s="10" t="inlineStr">
         <is>
-          <t>26-0103-0006</t>
+          <t>25-0927-0018</t>
         </is>
       </c>
       <c r="L52" s="11" t="inlineStr">
@@ -3649,75 +2775,33 @@
       </c>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Altea</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>36" x 80"</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>Matte Black</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E53" s="9" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="F53" s="10">
-        <f>COUNTIFS($A:$A,A53,$B:$B,B53,$C:$C,C53,$D:$D,D53,$E:$E,E53,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G53" s="10">
-        <f>COUNTIFS($A:$A,A53,$B:$B,B53,$C:$C,C53,$D:$D,D53,$E:$E,E53,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H53" s="10">
-        <f>COUNTIFS($A:$A,A53,$B:$B,B53,$C:$C,C53,$D:$D,D53,$E:$E,E53,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I53" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="J53" s="10">
-        <f>F53+G53+H53-I53</f>
-        <v/>
-      </c>
-      <c r="K53" s="10" t="inlineStr">
-        <is>
-          <t>26-0103-0007</t>
-        </is>
-      </c>
-      <c r="L53" s="11" t="inlineStr">
-        <is>
-          <t>In Stock</t>
-        </is>
-      </c>
+      <c r="A53" s="16" t="n"/>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="17" t="n"/>
+      <c r="G53" s="17" t="n"/>
+      <c r="H53" s="17" t="n"/>
+      <c r="I53" s="17" t="n"/>
+      <c r="J53" s="17" t="n"/>
+      <c r="K53" s="17" t="n"/>
+      <c r="L53" s="18" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>Altea</t>
+          <t>Granada</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>36" x 80"</t>
+          <t>36" x 96"</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Matte Black</t>
+          <t>Satin White</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
@@ -3727,7 +2811,7 @@
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Sidelite</t>
         </is>
       </c>
       <c r="F54" s="10">
@@ -3743,7 +2827,7 @@
         <v/>
       </c>
       <c r="I54" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J54" s="10">
         <f>F54+G54+H54-I54</f>
@@ -3751,7 +2835,7 @@
       </c>
       <c r="K54" s="10" t="inlineStr">
         <is>
-          <t>26-0103-0008</t>
+          <t>25-0927-0019</t>
         </is>
       </c>
       <c r="L54" s="11" t="inlineStr">
@@ -3763,66 +2847,758 @@
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="12" t="inlineStr">
         <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>36" x 96"</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>Sidelite</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="n"/>
+      <c r="G55" s="14" t="n"/>
+      <c r="H55" s="14" t="n"/>
+      <c r="I55" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="J55" s="14" t="n"/>
+      <c r="K55" s="14" t="inlineStr">
+        <is>
+          <t>25-0927-0020</t>
+        </is>
+      </c>
+      <c r="L55" s="15" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="n"/>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
+      <c r="G56" s="17" t="n"/>
+      <c r="H56" s="17" t="n"/>
+      <c r="I56" s="17" t="n"/>
+      <c r="J56" s="17" t="n"/>
+      <c r="K56" s="17" t="n"/>
+      <c r="L56" s="17" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="n"/>
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="17" t="n"/>
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="17" t="n"/>
+      <c r="I57" s="17" t="n"/>
+      <c r="J57" s="17" t="n"/>
+      <c r="K57" s="17" t="n"/>
+      <c r="L57" s="17" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F58" s="6">
+        <f>COUNTIFS($A:$A,A58,$B:$B,B58,$C:$C,C58,$D:$D,D58,$E:$E,E58,$L:$L,"In Stock")</f>
+        <v/>
+      </c>
+      <c r="G58" s="6">
+        <f>COUNTIFS($A:$A,A58,$B:$B,B58,$C:$C,C58,$D:$D,D58,$E:$E,E58,$L:$L,"In Production")</f>
+        <v/>
+      </c>
+      <c r="H58" s="6">
+        <f>COUNTIFS($A:$A,A58,$B:$B,B58,$C:$C,C58,$D:$D,D58,$E:$E,E58,$L:$L,"Pre-Sale")</f>
+        <v/>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J58" s="6">
+        <f>F58+G58+H58-I58</f>
+        <v/>
+      </c>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>25-1205-0021</t>
+        </is>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C59" s="9" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E59" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F59" s="10" t="n"/>
+      <c r="G59" s="10" t="n"/>
+      <c r="H59" s="10" t="n"/>
+      <c r="I59" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J59" s="10" t="n"/>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>25-1205-0022</t>
+        </is>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F60" s="10" t="n"/>
+      <c r="G60" s="10" t="n"/>
+      <c r="H60" s="10" t="n"/>
+      <c r="I60" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J60" s="10" t="n"/>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>25-1205-0023</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="B61" s="13" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>Brushed Nickel</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F61" s="14" t="n"/>
+      <c r="G61" s="14" t="n"/>
+      <c r="H61" s="14" t="n"/>
+      <c r="I61" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J61" s="14" t="n"/>
+      <c r="K61" s="14" t="inlineStr">
+        <is>
+          <t>25-1205-0024</t>
+        </is>
+      </c>
+      <c r="L61" s="15" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="17" t="n"/>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
+      <c r="F62" s="17" t="n"/>
+      <c r="G62" s="17" t="n"/>
+      <c r="H62" s="17" t="n"/>
+      <c r="I62" s="17" t="n"/>
+      <c r="J62" s="17" t="n"/>
+      <c r="K62" s="17" t="n"/>
+      <c r="L62" s="17" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="n"/>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="F63" s="17" t="n"/>
+      <c r="G63" s="17" t="n"/>
+      <c r="H63" s="17" t="n"/>
+      <c r="I63" s="17" t="n"/>
+      <c r="J63" s="17" t="n"/>
+      <c r="K63" s="17" t="n"/>
+      <c r="L63" s="17" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
           <t>Altea</t>
         </is>
       </c>
-      <c r="B55" s="13" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F64" s="6">
+        <f>COUNTIFS($A:$A,A64,$B:$B,B64,$C:$C,C64,$D:$D,D64,$E:$E,E64,$L:$L,"In Stock")</f>
+        <v/>
+      </c>
+      <c r="G64" s="6">
+        <f>COUNTIFS($A:$A,A64,$B:$B,B64,$C:$C,C64,$D:$D,D64,$E:$E,E64,$L:$L,"In Production")</f>
+        <v/>
+      </c>
+      <c r="H64" s="6">
+        <f>COUNTIFS($A:$A,A64,$B:$B,B64,$C:$C,C64,$D:$D,D64,$E:$E,E64,$L:$L,"Pre-Sale")</f>
+        <v/>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="J64" s="6">
+        <f>F64+G64+H64-I64</f>
+        <v/>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>26-0103-0001</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C65" s="9" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="n"/>
+      <c r="G65" s="10" t="n"/>
+      <c r="H65" s="10" t="n"/>
+      <c r="I65" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J65" s="10" t="n"/>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>26-0103-0002</t>
+        </is>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F66" s="10" t="n"/>
+      <c r="G66" s="10" t="n"/>
+      <c r="H66" s="10" t="n"/>
+      <c r="I66" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J66" s="10" t="n"/>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>26-0103-0003</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F67" s="10" t="n"/>
+      <c r="G67" s="10" t="n"/>
+      <c r="H67" s="10" t="n"/>
+      <c r="I67" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J67" s="10" t="n"/>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>26-0103-0004</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>32" x 80"</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>Satin White</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Right Inswing</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>Clear</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="n"/>
+      <c r="G68" s="10" t="n"/>
+      <c r="H68" s="10" t="n"/>
+      <c r="I68" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J68" s="10" t="n"/>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>26-0103-0005</t>
+        </is>
+      </c>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="n"/>
+      <c r="B69" s="17" t="n"/>
+      <c r="C69" s="17" t="n"/>
+      <c r="D69" s="17" t="n"/>
+      <c r="E69" s="17" t="n"/>
+      <c r="F69" s="17" t="n"/>
+      <c r="G69" s="17" t="n"/>
+      <c r="H69" s="17" t="n"/>
+      <c r="I69" s="17" t="n"/>
+      <c r="J69" s="17" t="n"/>
+      <c r="K69" s="17" t="n"/>
+      <c r="L69" s="18" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F70" s="10">
+        <f>COUNTIFS($A:$A,A70,$B:$B,B70,$C:$C,C70,$D:$D,D70,$E:$E,E70,$L:$L,"In Stock")</f>
+        <v/>
+      </c>
+      <c r="G70" s="10">
+        <f>COUNTIFS($A:$A,A70,$B:$B,B70,$C:$C,C70,$D:$D,D70,$E:$E,E70,$L:$L,"In Production")</f>
+        <v/>
+      </c>
+      <c r="H70" s="10">
+        <f>COUNTIFS($A:$A,A70,$B:$B,B70,$C:$C,C70,$D:$D,D70,$E:$E,E70,$L:$L,"Pre-Sale")</f>
+        <v/>
+      </c>
+      <c r="I70" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J70" s="10">
+        <f>F70+G70+H70-I70</f>
+        <v/>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>26-0103-0006</t>
+        </is>
+      </c>
+      <c r="L70" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F71" s="10" t="n"/>
+      <c r="G71" s="10" t="n"/>
+      <c r="H71" s="10" t="n"/>
+      <c r="I71" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J71" s="10" t="n"/>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>26-0103-0007</t>
+        </is>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>36" x 80"</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>Matte Black</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="inlineStr">
+        <is>
+          <t>Rain</t>
+        </is>
+      </c>
+      <c r="F72" s="10" t="n"/>
+      <c r="G72" s="10" t="n"/>
+      <c r="H72" s="10" t="n"/>
+      <c r="I72" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J72" s="10" t="n"/>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>26-0103-0008</t>
+        </is>
+      </c>
+      <c r="L72" s="11" t="inlineStr">
+        <is>
+          <t>In Stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="n"/>
+      <c r="B73" s="17" t="n"/>
+      <c r="C73" s="17" t="n"/>
+      <c r="D73" s="17" t="n"/>
+      <c r="E73" s="17" t="n"/>
+      <c r="F73" s="17" t="n"/>
+      <c r="G73" s="17" t="n"/>
+      <c r="H73" s="17" t="n"/>
+      <c r="I73" s="17" t="n"/>
+      <c r="J73" s="17" t="n"/>
+      <c r="K73" s="17" t="n"/>
+      <c r="L73" s="18" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>Altea</t>
+        </is>
+      </c>
+      <c r="B74" s="13" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C55" s="13" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D55" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E55" s="13" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
       </c>
-      <c r="F55" s="14">
-        <f>COUNTIFS($A:$A,A55,$B:$B,B55,$C:$C,C55,$D:$D,D55,$E:$E,E55,$L:$L,"In Stock")</f>
-        <v/>
-      </c>
-      <c r="G55" s="14">
-        <f>COUNTIFS($A:$A,A55,$B:$B,B55,$C:$C,C55,$D:$D,D55,$E:$E,E55,$L:$L,"In Production")</f>
-        <v/>
-      </c>
-      <c r="H55" s="14">
-        <f>COUNTIFS($A:$A,A55,$B:$B,B55,$C:$C,C55,$D:$D,D55,$E:$E,E55,$L:$L,"Pre-Sale")</f>
-        <v/>
-      </c>
-      <c r="I55" s="14" t="n">
+      <c r="F74" s="14">
+        <f>COUNTIFS($A:$A,A74,$B:$B,B74,$C:$C,C74,$D:$D,D74,$E:$E,E74,$L:$L,"In Stock")</f>
+        <v/>
+      </c>
+      <c r="G74" s="14">
+        <f>COUNTIFS($A:$A,A74,$B:$B,B74,$C:$C,C74,$D:$D,D74,$E:$E,E74,$L:$L,"In Production")</f>
+        <v/>
+      </c>
+      <c r="H74" s="14">
+        <f>COUNTIFS($A:$A,A74,$B:$B,B74,$C:$C,C74,$D:$D,D74,$E:$E,E74,$L:$L,"Pre-Sale")</f>
+        <v/>
+      </c>
+      <c r="I74" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="J55" s="14">
-        <f>F55+G55+H55-I55</f>
-        <v/>
-      </c>
-      <c r="K55" s="14" t="inlineStr">
+      <c r="J74" s="14">
+        <f>F74+G74+H74-I74</f>
+        <v/>
+      </c>
+      <c r="K74" s="14" t="inlineStr">
         <is>
           <t>26-0415-0009</t>
         </is>
       </c>
-      <c r="L55" s="15" t="inlineStr">
+      <c r="L74" s="15" t="inlineStr">
         <is>
           <t>In Stock</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J2:J55">
+  <conditionalFormatting sqref="J3:J74">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="4">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L55">
+  <conditionalFormatting sqref="L3:L74">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="5">
       <formula>"In Stock"</formula>
     </cfRule>
@@ -3833,7 +3609,7 @@
       <formula>"In Production"</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="8">
-      <formula>=LEFT($L2,9)="Allocated"</formula>
+      <formula>=LEFT($L3,9)="Allocated"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/inventory_master.xlsx
+++ b/inventory_master.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +47,12 @@
     <font>
       <name val="Arial"/>
       <color rgb="FFFF0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -356,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -541,6 +547,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1062,27 +1080,27 @@
       <c r="L2" s="24" t="n"/>
     </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="66" t="inlineStr">
+      <c r="A3" s="70" t="inlineStr">
         <is>
           <t>Altea Double Door</t>
         </is>
       </c>
-      <c r="B3" s="67" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C3" s="67" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D3" s="67" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E3" s="67" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1294,27 +1312,27 @@
       <c r="L8" s="39" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="72" t="inlineStr">
         <is>
           <t>Altea Double Door</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="73" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="73" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="D9" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E9" s="73" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -1602,27 +1620,27 @@
       <c r="L16" s="39" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="72" t="inlineStr">
         <is>
           <t>Altea Double Door</t>
         </is>
       </c>
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="73" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="73" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="73" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="73" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
@@ -1666,27 +1684,27 @@
       <c r="L18" s="39" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="34" t="inlineStr">
+      <c r="A19" s="72" t="inlineStr">
         <is>
           <t>Altea Double Door</t>
         </is>
       </c>
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="73" t="inlineStr">
         <is>
           <t>72" x 80"</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="73" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="D19" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E19" s="73" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -1870,27 +1888,27 @@
       <c r="L24" s="42" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="66" t="inlineStr">
+      <c r="A25" s="70" t="inlineStr">
         <is>
           <t>Cordova Sliding Window</t>
         </is>
       </c>
-      <c r="B25" s="67" t="inlineStr">
+      <c r="B25" s="71" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C25" s="67" t="inlineStr">
+      <c r="C25" s="71" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D25" s="67" t="inlineStr">
+      <c r="D25" s="71" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E25" s="67" t="inlineStr">
+      <c r="E25" s="71" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -2144,27 +2162,27 @@
       <c r="L31" s="39" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="34" t="inlineStr">
+      <c r="A32" s="72" t="inlineStr">
         <is>
           <t>Cordova Sliding Window</t>
         </is>
       </c>
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="73" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="C32" s="73" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D32" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E32" s="35" t="inlineStr">
+      <c r="D32" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E32" s="73" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2292,27 +2310,27 @@
       <c r="L35" s="39" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="A36" s="72" t="inlineStr">
         <is>
           <t>Cordova Sliding Window</t>
         </is>
       </c>
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="73" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="C36" s="73" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D36" s="73" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E36" s="35" t="inlineStr">
+      <c r="E36" s="73" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -2356,27 +2374,27 @@
       <c r="L37" s="39" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="34" t="inlineStr">
+      <c r="A38" s="72" t="inlineStr">
         <is>
           <t>Cordova Sliding Window</t>
         </is>
       </c>
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="73" t="inlineStr">
         <is>
           <t>48" x 36"</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C38" s="73" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D38" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="D38" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E38" s="73" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -2896,27 +2914,27 @@
       <c r="L51" s="42" t="n"/>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="66" t="inlineStr">
+      <c r="A52" s="70" t="inlineStr">
         <is>
           <t>Granada Bi-fold Door</t>
         </is>
       </c>
-      <c r="B52" s="67" t="inlineStr">
+      <c r="B52" s="71" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C52" s="67" t="inlineStr">
+      <c r="C52" s="71" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D52" s="67" t="inlineStr">
+      <c r="D52" s="71" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E52" s="67" t="inlineStr">
+      <c r="E52" s="71" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -3254,27 +3272,27 @@
       <c r="L60" s="39" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="34" t="inlineStr">
+      <c r="A61" s="72" t="inlineStr">
         <is>
           <t>Granada Bi-fold Door</t>
         </is>
       </c>
-      <c r="B61" s="35" t="inlineStr">
+      <c r="B61" s="73" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C61" s="35" t="inlineStr">
+      <c r="C61" s="73" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D61" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E61" s="35" t="inlineStr">
+      <c r="D61" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E61" s="73" t="inlineStr">
         <is>
           <t>Sidelite</t>
         </is>
@@ -3360,27 +3378,27 @@
       <c r="L63" s="39" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="34" t="inlineStr">
+      <c r="A64" s="72" t="inlineStr">
         <is>
           <t>Granada Bi-fold Door</t>
         </is>
       </c>
-      <c r="B64" s="35" t="inlineStr">
+      <c r="B64" s="73" t="inlineStr">
         <is>
           <t>96" x 80"</t>
         </is>
       </c>
-      <c r="C64" s="35" t="inlineStr">
+      <c r="C64" s="73" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E64" s="35" t="inlineStr">
+      <c r="D64" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E64" s="73" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -3522,27 +3540,27 @@
       <c r="L68" s="42" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="66" t="inlineStr">
+      <c r="A69" s="70" t="inlineStr">
         <is>
           <t>Malaga Single Door</t>
         </is>
       </c>
-      <c r="B69" s="67" t="inlineStr">
+      <c r="B69" s="71" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C69" s="67" t="inlineStr">
+      <c r="C69" s="71" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D69" s="67" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E69" s="67" t="inlineStr">
+      <c r="D69" s="71" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E69" s="71" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -3712,27 +3730,27 @@
       <c r="L73" s="39" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="34" t="inlineStr">
+      <c r="A74" s="72" t="inlineStr">
         <is>
           <t>Malaga Single Door</t>
         </is>
       </c>
-      <c r="B74" s="35" t="inlineStr">
+      <c r="B74" s="73" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C74" s="35" t="inlineStr">
+      <c r="C74" s="73" t="inlineStr">
         <is>
           <t>Gunmetal</t>
         </is>
       </c>
-      <c r="D74" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E74" s="35" t="inlineStr">
+      <c r="D74" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E74" s="73" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4378,27 +4396,27 @@
       <c r="L90" s="42" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="66" t="inlineStr">
+      <c r="A91" s="70" t="inlineStr">
         <is>
           <t>Sevilla French Door</t>
         </is>
       </c>
-      <c r="B91" s="67" t="inlineStr">
+      <c r="B91" s="71" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C91" s="67" t="inlineStr">
+      <c r="C91" s="71" t="inlineStr">
         <is>
           <t>Brushed Nickel</t>
         </is>
       </c>
-      <c r="D91" s="67" t="inlineStr">
+      <c r="D91" s="71" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E91" s="67" t="inlineStr">
+      <c r="E91" s="71" t="inlineStr">
         <is>
           <t>Rain</t>
         </is>
@@ -4610,27 +4628,27 @@
       <c r="L96" s="39" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="34" t="inlineStr">
+      <c r="A97" s="72" t="inlineStr">
         <is>
           <t>Sevilla French Door</t>
         </is>
       </c>
-      <c r="B97" s="35" t="inlineStr">
+      <c r="B97" s="73" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C97" s="35" t="inlineStr">
+      <c r="C97" s="73" t="inlineStr">
         <is>
           <t>Satin White</t>
         </is>
       </c>
-      <c r="D97" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E97" s="35" t="inlineStr">
+      <c r="D97" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E97" s="73" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -4918,27 +4936,27 @@
       <c r="L104" s="39" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="34" t="inlineStr">
+      <c r="A105" s="72" t="inlineStr">
         <is>
           <t>Sevilla French Door</t>
         </is>
       </c>
-      <c r="B105" s="35" t="inlineStr">
+      <c r="B105" s="73" t="inlineStr">
         <is>
           <t>72" x 80"</t>
         </is>
       </c>
-      <c r="C105" s="35" t="inlineStr">
+      <c r="C105" s="73" t="inlineStr">
         <is>
           <t>Matte White</t>
         </is>
       </c>
-      <c r="D105" s="35" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E105" s="35" t="inlineStr">
+      <c r="D105" s="73" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E105" s="73" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
@@ -5164,27 +5182,27 @@
       <c r="L111" s="42" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="66" t="inlineStr">
+      <c r="A112" s="70" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B112" s="67" t="inlineStr">
+      <c r="B112" s="71" t="inlineStr">
         <is>
           <t>32" x 80"</t>
         </is>
       </c>
-      <c r="C112" s="67" t="inlineStr">
+      <c r="C112" s="71" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D112" s="67" t="inlineStr">
-        <is>
-          <t>Left Inswing</t>
-        </is>
-      </c>
-      <c r="E112" s="67" t="inlineStr">
+      <c r="D112" s="71" t="inlineStr">
+        <is>
+          <t>Left Inswing</t>
+        </is>
+      </c>
+      <c r="E112" s="71" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -5594,27 +5612,27 @@
       <c r="L122" s="39" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="34" t="inlineStr">
+      <c r="A123" s="72" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B123" s="35" t="inlineStr">
+      <c r="B123" s="73" t="inlineStr">
         <is>
           <t>36" x 80"</t>
         </is>
       </c>
-      <c r="C123" s="35" t="inlineStr">
+      <c r="C123" s="73" t="inlineStr">
         <is>
           <t>Matte Black</t>
         </is>
       </c>
-      <c r="D123" s="35" t="inlineStr">
+      <c r="D123" s="73" t="inlineStr">
         <is>
           <t>Right Inswing</t>
         </is>
       </c>
-      <c r="E123" s="35" t="inlineStr">
+      <c r="E123" s="73" t="inlineStr">
         <is>
           <t>Clear</t>
         </is>
@@ -5910,27 +5928,27 @@
       <c r="L130" s="39" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="34" t="inlineStr">
+      <c r="A131" s="72" t="inlineStr">
         <is>
           <t>Valencia Single Door</t>
         </is>
       </c>
-      <c r="B131" s="35" t="inlineStr">
+      <c r="B131" s="73" t="inlineStr">
         <is>
           <t>36" x 96"</t>
         </is>
       </c>
-      <c r="C131" s="35" t="inlineStr">
+      <c r="C131" s="73" t="inlineStr">
         <is>
           <t>Oil-Rubbed Bronze</t>
         </is>
       </c>
-      <c r="D131" s="35" t="inlineStr">
+      <c r="D131" s="73" t="inlineStr">
         <is>
           <t>Right Outswing</t>
         </is>
       </c>
-      <c r="E131" s="35" t="inlineStr">
+      <c r="E131" s="73" t="inlineStr">
         <is>
           <t>Frosted</t>
         </is>
